--- a/99 - Excels/LP-Register.xlsx
+++ b/99 - Excels/LP-Register.xlsx
@@ -1,16 +1,16 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
 <workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr6="http://schemas.microsoft.com/office/spreadsheetml/2016/revision6" xmlns:xr10="http://schemas.microsoft.com/office/spreadsheetml/2016/revision10" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" mc:Ignorable="x15 xr xr6 xr10 xr2">
-  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="29127"/>
+  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="30228"/>
   <workbookPr/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
-      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\feb3ct\Desktop\PyAutomateSAP\99 - Excels\"/>
+      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\Mao8ct\Desktop\PyAutomateSAP\99 - Excels\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{FCAB4FED-1ED7-46D1-AF48-D2A5B015ED57}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{BBD7E14E-02B5-4F81-9C81-12846806D476}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="-120" yWindow="-120" windowWidth="29040" windowHeight="15720" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
+    <workbookView xWindow="-120" yWindow="-120" windowWidth="29040" windowHeight="17520" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
   <sheets>
     <sheet name="Sheet1" sheetId="1" r:id="rId1"/>
@@ -23,7 +23,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="567" uniqueCount="255">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="707" uniqueCount="318">
   <si>
     <t>Responsável</t>
   </si>
@@ -70,9 +70,6 @@
     <t>SO/OPM-TS23-BR</t>
   </si>
   <si>
-    <t>Liberado</t>
-  </si>
-  <si>
     <t>685072</t>
   </si>
   <si>
@@ -568,226 +565,418 @@
     <t>SOC2CT</t>
   </si>
   <si>
-    <t>LP055141</t>
-  </si>
-  <si>
-    <t>LP055184</t>
-  </si>
-  <si>
-    <t>LP056109</t>
-  </si>
-  <si>
-    <t>LP055213</t>
-  </si>
-  <si>
-    <t>LP055299</t>
-  </si>
-  <si>
-    <t>LP055311</t>
-  </si>
-  <si>
-    <t>LP055312</t>
-  </si>
-  <si>
-    <t>LP055309</t>
-  </si>
-  <si>
-    <t>LP055508</t>
-  </si>
-  <si>
-    <t>LP055454</t>
-  </si>
-  <si>
-    <t>LP055455</t>
-  </si>
-  <si>
-    <t>LP055456</t>
-  </si>
-  <si>
-    <t>LP055426</t>
-  </si>
-  <si>
-    <t>LP055485</t>
-  </si>
-  <si>
-    <t>LP055486</t>
-  </si>
-  <si>
-    <t>LP055425</t>
-  </si>
-  <si>
-    <t>LP055584</t>
-  </si>
-  <si>
-    <t>LP056010</t>
-  </si>
-  <si>
-    <t>LP055465</t>
-  </si>
-  <si>
-    <t>LP055459</t>
-  </si>
-  <si>
-    <t>LP055490</t>
-  </si>
-  <si>
-    <t>LP055491</t>
-  </si>
-  <si>
-    <t>LP055525</t>
-  </si>
-  <si>
-    <t>LP055560</t>
-  </si>
-  <si>
-    <t>LP055514</t>
-  </si>
-  <si>
-    <t>LP055587</t>
-  </si>
-  <si>
-    <t>LP055588</t>
-  </si>
-  <si>
-    <t>LP055529</t>
-  </si>
-  <si>
-    <t>LP055693</t>
-  </si>
-  <si>
-    <t>LP056199</t>
-  </si>
-  <si>
-    <t>LP055632</t>
-  </si>
-  <si>
-    <t>LP055635</t>
-  </si>
-  <si>
-    <t>LP055773</t>
-  </si>
-  <si>
-    <t>LP055858</t>
-  </si>
-  <si>
-    <t>LP055937</t>
-  </si>
-  <si>
-    <t>LP056066</t>
-  </si>
-  <si>
-    <t>LP056067</t>
-  </si>
-  <si>
-    <t>LP055998</t>
-  </si>
-  <si>
-    <t>LP056028</t>
-  </si>
-  <si>
-    <t>LP056029</t>
-  </si>
-  <si>
-    <t>LP056030</t>
-  </si>
-  <si>
-    <t>LP056170</t>
-  </si>
-  <si>
-    <t>LP056299</t>
-  </si>
-  <si>
-    <t>LP056300</t>
-  </si>
-  <si>
-    <t>LP056231</t>
-  </si>
-  <si>
-    <t>LP056275</t>
-  </si>
-  <si>
-    <t>LP056627</t>
-  </si>
-  <si>
-    <t>LP056567</t>
-  </si>
-  <si>
-    <t>LP056854</t>
-  </si>
-  <si>
-    <t>LP056762</t>
-  </si>
-  <si>
-    <t>LP057055</t>
-  </si>
-  <si>
-    <t>LP056872</t>
-  </si>
-  <si>
-    <t>LP056873</t>
-  </si>
-  <si>
-    <t>LP057095</t>
-  </si>
-  <si>
-    <t>LP057071</t>
-  </si>
-  <si>
-    <t>LP057030</t>
-  </si>
-  <si>
-    <t>LP057031</t>
-  </si>
-  <si>
-    <t>LP057032</t>
-  </si>
-  <si>
-    <t>LP057029</t>
-  </si>
-  <si>
-    <t>LP057070</t>
-  </si>
-  <si>
-    <t>LP057481</t>
-  </si>
-  <si>
-    <t>LP057178</t>
-  </si>
-  <si>
-    <t>LP057188</t>
-  </si>
-  <si>
-    <t>LP057189</t>
-  </si>
-  <si>
-    <t>LP057243</t>
-  </si>
-  <si>
-    <t>LP057471</t>
-  </si>
-  <si>
-    <t>LP057549</t>
-  </si>
-  <si>
-    <t>LP057572</t>
-  </si>
-  <si>
-    <t>LP057739</t>
-  </si>
-  <si>
-    <t>LP057728</t>
-  </si>
-  <si>
-    <t>LP057722</t>
-  </si>
-  <si>
-    <t>LP057866</t>
-  </si>
-  <si>
-    <t>LP057849</t>
-  </si>
-  <si>
-    <t>LP059536</t>
+    <t>19</t>
+  </si>
+  <si>
+    <t>LP-055141</t>
+  </si>
+  <si>
+    <t>LP-055184</t>
+  </si>
+  <si>
+    <t>LP-056109</t>
+  </si>
+  <si>
+    <t>05</t>
+  </si>
+  <si>
+    <t>LP-055213</t>
+  </si>
+  <si>
+    <t>LP-055299</t>
+  </si>
+  <si>
+    <t>LP-055311</t>
+  </si>
+  <si>
+    <t>LP-055312</t>
+  </si>
+  <si>
+    <t/>
+  </si>
+  <si>
+    <t>LP-055309</t>
+  </si>
+  <si>
+    <t>LP-055508</t>
+  </si>
+  <si>
+    <t>LP-055454</t>
+  </si>
+  <si>
+    <t>LP-055455</t>
+  </si>
+  <si>
+    <t>LP-055456</t>
+  </si>
+  <si>
+    <t>N/A</t>
+  </si>
+  <si>
+    <t>LP-055426</t>
+  </si>
+  <si>
+    <t>LP-055485</t>
+  </si>
+  <si>
+    <t>LP-055486</t>
+  </si>
+  <si>
+    <t>LP-055425</t>
+  </si>
+  <si>
+    <t>LP-055584</t>
+  </si>
+  <si>
+    <t>LP-056010</t>
+  </si>
+  <si>
+    <t>LP-055465</t>
+  </si>
+  <si>
+    <t>LP-055459</t>
+  </si>
+  <si>
+    <t>LP-055490</t>
+  </si>
+  <si>
+    <t>LP-055491</t>
+  </si>
+  <si>
+    <t>LP-055525</t>
+  </si>
+  <si>
+    <t>LP-055560</t>
+  </si>
+  <si>
+    <t>LP-055514</t>
+  </si>
+  <si>
+    <t>LP-055587</t>
+  </si>
+  <si>
+    <t>LP-055588</t>
+  </si>
+  <si>
+    <t>NA</t>
+  </si>
+  <si>
+    <t>LP-055529</t>
+  </si>
+  <si>
+    <t>LP-055693</t>
+  </si>
+  <si>
+    <t>03</t>
+  </si>
+  <si>
+    <t>LP-056199</t>
+  </si>
+  <si>
+    <t>LP-055632</t>
+  </si>
+  <si>
+    <t>LP-055635</t>
+  </si>
+  <si>
+    <t>LP-055773</t>
+  </si>
+  <si>
+    <t>LP-055858</t>
+  </si>
+  <si>
+    <t>LP-055937</t>
+  </si>
+  <si>
+    <t>LP-056066</t>
+  </si>
+  <si>
+    <t>LP-056067</t>
+  </si>
+  <si>
+    <t>LP-055998</t>
+  </si>
+  <si>
+    <t>LP-056028</t>
+  </si>
+  <si>
+    <t>LP-056029</t>
+  </si>
+  <si>
+    <t>LP-056030</t>
+  </si>
+  <si>
+    <t>LP-056170</t>
+  </si>
+  <si>
+    <t>LP-056299</t>
+  </si>
+  <si>
+    <t>LP-056300</t>
+  </si>
+  <si>
+    <t>LP-056231</t>
+  </si>
+  <si>
+    <t>12</t>
+  </si>
+  <si>
+    <t>LP-056275</t>
+  </si>
+  <si>
+    <t>LP-056627</t>
+  </si>
+  <si>
+    <t>LP-056567</t>
+  </si>
+  <si>
+    <t>LP-056854</t>
+  </si>
+  <si>
+    <t>LP-056762</t>
+  </si>
+  <si>
+    <t>LP-057055</t>
+  </si>
+  <si>
+    <t>LP-056872</t>
+  </si>
+  <si>
+    <t>LP-056873</t>
+  </si>
+  <si>
+    <t>LP-057095</t>
+  </si>
+  <si>
+    <t>LP-057071</t>
+  </si>
+  <si>
+    <t>LP-057030</t>
+  </si>
+  <si>
+    <t>LP-057031</t>
+  </si>
+  <si>
+    <t>LP-057032</t>
+  </si>
+  <si>
+    <t>LP-057029</t>
+  </si>
+  <si>
+    <t>LP-057070</t>
+  </si>
+  <si>
+    <t>LP-057481</t>
+  </si>
+  <si>
+    <t>LP-057178</t>
+  </si>
+  <si>
+    <t>LP-057188</t>
+  </si>
+  <si>
+    <t>LP-057189</t>
+  </si>
+  <si>
+    <t>LP-057243</t>
+  </si>
+  <si>
+    <t>LP-057471</t>
+  </si>
+  <si>
+    <t>LP-057549</t>
+  </si>
+  <si>
+    <t>LP-057572</t>
+  </si>
+  <si>
+    <t>LP-057739</t>
+  </si>
+  <si>
+    <t>LP-057728</t>
+  </si>
+  <si>
+    <t>06</t>
+  </si>
+  <si>
+    <t>LP-057722</t>
+  </si>
+  <si>
+    <t>LP-057866</t>
+  </si>
+  <si>
+    <t>LP-057849</t>
+  </si>
+  <si>
+    <t>LP-059536</t>
+  </si>
+  <si>
+    <t>685622</t>
+  </si>
+  <si>
+    <t>4729111277</t>
+  </si>
+  <si>
+    <t xml:space="preserve"> CARRINHOS DE TRANSPORTE EMAG</t>
+  </si>
+  <si>
+    <t>LP-059949</t>
+  </si>
+  <si>
+    <t>Rodrigo Melo</t>
+  </si>
+  <si>
+    <t>685485</t>
+  </si>
+  <si>
+    <t>04</t>
+  </si>
+  <si>
+    <t>4716406346-0005</t>
+  </si>
+  <si>
+    <t>LX - Conserto</t>
+  </si>
+  <si>
+    <t>QMM</t>
+  </si>
+  <si>
+    <t>PS/QMM7-CtP</t>
+  </si>
+  <si>
+    <t>LP-059953</t>
+  </si>
+  <si>
+    <t>4716510509-0004</t>
+  </si>
+  <si>
+    <t>LY - conserto</t>
+  </si>
+  <si>
+    <t>LP-059955</t>
+  </si>
+  <si>
+    <t>4716510509-0005</t>
+  </si>
+  <si>
+    <t>LP-059954</t>
+  </si>
+  <si>
+    <t>Yesica Gonzalez</t>
+  </si>
+  <si>
+    <t>685421</t>
+  </si>
+  <si>
+    <t>20</t>
+  </si>
+  <si>
+    <t>4712001379</t>
+  </si>
+  <si>
+    <t>DU 685421 Conexão de usinagem HE</t>
+  </si>
+  <si>
+    <t>DONI- 2803</t>
+  </si>
+  <si>
+    <t>LP-059940</t>
+  </si>
+  <si>
+    <t>Marcelo Simoes</t>
+  </si>
+  <si>
+    <t>685553</t>
+  </si>
+  <si>
+    <t>4712003897</t>
+  </si>
+  <si>
+    <t>Posição 2</t>
+  </si>
+  <si>
+    <t>LP-059946</t>
+  </si>
+  <si>
+    <t>Retrabalho buchas guias do varão</t>
+  </si>
+  <si>
+    <t>JOAO</t>
+  </si>
+  <si>
+    <t>LP-059947</t>
+  </si>
+  <si>
+    <t>685178</t>
+  </si>
+  <si>
+    <t>FABRICAÇÃO PROTOTIPO SUPORTE</t>
+  </si>
+  <si>
+    <t>LP-059948</t>
+  </si>
+  <si>
+    <t>685541</t>
+  </si>
+  <si>
+    <t>10</t>
+  </si>
+  <si>
+    <t>Pinças projeto naka</t>
+  </si>
+  <si>
+    <t>EZAU MALINOS</t>
+  </si>
+  <si>
+    <t>LP-059944</t>
+  </si>
+  <si>
+    <t>685070</t>
+  </si>
+  <si>
+    <t>DISPOSITIVO BATIDAS V3</t>
+  </si>
+  <si>
+    <t>SIU5CT</t>
+  </si>
+  <si>
+    <t>LP-059951</t>
+  </si>
+  <si>
+    <t>4702500326</t>
+  </si>
+  <si>
+    <t>PINO DE CONTATO ELETRODO</t>
+  </si>
+  <si>
+    <t>LP-059957</t>
+  </si>
+  <si>
+    <t>Thais Fischer</t>
+  </si>
+  <si>
+    <t>685868</t>
+  </si>
+  <si>
+    <t>PINO ZOLLER ISO40</t>
+  </si>
+  <si>
+    <t>ANA LUZ</t>
+  </si>
+  <si>
+    <t>LP-059956</t>
+  </si>
+  <si>
+    <t>4710800100</t>
+  </si>
+  <si>
+    <t>Retrabalho contra-ponto</t>
+  </si>
+  <si>
+    <t>CLEYSON</t>
+  </si>
+  <si>
+    <t>LP-059950</t>
   </si>
 </sst>
 </file>
@@ -1150,10 +1339,10 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0000-000000000000}">
-  <dimension ref="A1:K75"/>
+  <dimension ref="A1:K88"/>
   <sheetFormatPr defaultRowHeight="15" x14ac:dyDescent="0.25"/>
   <cols>
-    <col min="1" max="1" width="12.85546875" bestFit="1" customWidth="1"/>
+    <col min="1" max="1" width="15.140625" bestFit="1" customWidth="1"/>
     <col min="2" max="2" width="26.140625" bestFit="1" customWidth="1"/>
     <col min="3" max="3" width="20.28515625" bestFit="1" customWidth="1"/>
     <col min="4" max="4" width="11.42578125" bestFit="1" customWidth="1"/>
@@ -1163,7 +1352,7 @@
     <col min="8" max="8" width="21.5703125" bestFit="1" customWidth="1"/>
     <col min="9" max="9" width="14.85546875" bestFit="1" customWidth="1"/>
     <col min="10" max="10" width="13.42578125" bestFit="1" customWidth="1"/>
-    <col min="11" max="11" width="8.7109375" bestFit="1" customWidth="1"/>
+    <col min="11" max="11" width="6.42578125" bestFit="1" customWidth="1"/>
   </cols>
   <sheetData>
     <row r="1" spans="1:11" x14ac:dyDescent="0.25">
@@ -1203,28 +1392,28 @@
     </row>
     <row r="2" spans="1:11" x14ac:dyDescent="0.25">
       <c r="A2" t="s">
-        <v>21</v>
+        <v>20</v>
       </c>
       <c r="B2" t="s">
+        <v>41</v>
+      </c>
+      <c r="C2" t="s">
+        <v>180</v>
+      </c>
+      <c r="D2">
+        <v>1</v>
+      </c>
+      <c r="E2" t="s">
         <v>42</v>
       </c>
-      <c r="C2">
-        <v>19</v>
-      </c>
-      <c r="D2">
-        <v>1</v>
-      </c>
-      <c r="E2" t="s">
+      <c r="F2" t="s">
         <v>43</v>
       </c>
-      <c r="F2" t="s">
+      <c r="G2" t="s">
         <v>44</v>
       </c>
-      <c r="G2" t="s">
-        <v>45</v>
-      </c>
       <c r="H2" t="s">
-        <v>35</v>
+        <v>34</v>
       </c>
       <c r="I2">
         <v>380</v>
@@ -1232,34 +1421,31 @@
       <c r="J2" t="s">
         <v>181</v>
       </c>
-      <c r="K2" t="s">
-        <v>15</v>
-      </c>
     </row>
     <row r="3" spans="1:11" x14ac:dyDescent="0.25">
       <c r="A3" t="s">
-        <v>21</v>
+        <v>20</v>
       </c>
       <c r="B3" t="s">
-        <v>27</v>
-      </c>
-      <c r="C3">
-        <v>19</v>
+        <v>26</v>
+      </c>
+      <c r="C3" t="s">
+        <v>180</v>
       </c>
       <c r="D3">
         <v>2</v>
       </c>
       <c r="E3" t="s">
-        <v>30</v>
+        <v>29</v>
       </c>
       <c r="F3" t="s">
-        <v>48</v>
+        <v>47</v>
       </c>
       <c r="G3" t="s">
+        <v>27</v>
+      </c>
+      <c r="H3" t="s">
         <v>28</v>
-      </c>
-      <c r="H3" t="s">
-        <v>29</v>
       </c>
       <c r="I3">
         <v>500</v>
@@ -1267,34 +1453,31 @@
       <c r="J3" t="s">
         <v>182</v>
       </c>
-      <c r="K3" t="s">
-        <v>15</v>
-      </c>
     </row>
     <row r="4" spans="1:11" x14ac:dyDescent="0.25">
       <c r="A4" t="s">
-        <v>21</v>
+        <v>20</v>
       </c>
       <c r="B4" t="s">
-        <v>49</v>
-      </c>
-      <c r="C4">
-        <v>19</v>
+        <v>48</v>
+      </c>
+      <c r="C4" t="s">
+        <v>180</v>
       </c>
       <c r="D4">
         <v>6</v>
       </c>
       <c r="E4" t="s">
+        <v>49</v>
+      </c>
+      <c r="F4" t="s">
         <v>50</v>
       </c>
-      <c r="F4" t="s">
+      <c r="G4" t="s">
         <v>51</v>
       </c>
-      <c r="G4" t="s">
-        <v>52</v>
-      </c>
       <c r="H4" t="s">
-        <v>29</v>
+        <v>28</v>
       </c>
       <c r="I4">
         <v>400</v>
@@ -1302,66 +1485,60 @@
       <c r="J4" t="s">
         <v>183</v>
       </c>
-      <c r="K4" t="s">
-        <v>15</v>
-      </c>
     </row>
     <row r="5" spans="1:11" x14ac:dyDescent="0.25">
       <c r="A5" t="s">
-        <v>21</v>
+        <v>20</v>
       </c>
       <c r="B5" t="s">
-        <v>25</v>
-      </c>
-      <c r="C5">
-        <v>5</v>
+        <v>24</v>
+      </c>
+      <c r="C5" t="s">
+        <v>184</v>
       </c>
       <c r="D5">
         <v>5</v>
       </c>
       <c r="E5" t="s">
+        <v>21</v>
+      </c>
+      <c r="F5" t="s">
+        <v>46</v>
+      </c>
+      <c r="G5" t="s">
         <v>22</v>
       </c>
-      <c r="F5" t="s">
-        <v>47</v>
-      </c>
-      <c r="G5" t="s">
-        <v>23</v>
-      </c>
       <c r="H5" t="s">
-        <v>26</v>
+        <v>25</v>
       </c>
       <c r="I5">
         <v>600</v>
       </c>
       <c r="J5" t="s">
-        <v>184</v>
-      </c>
-      <c r="K5" t="s">
-        <v>15</v>
+        <v>185</v>
       </c>
     </row>
     <row r="6" spans="1:11" x14ac:dyDescent="0.25">
       <c r="A6" t="s">
-        <v>21</v>
+        <v>20</v>
       </c>
       <c r="B6" t="s">
+        <v>52</v>
+      </c>
+      <c r="C6" t="s">
+        <v>180</v>
+      </c>
+      <c r="D6">
+        <v>1</v>
+      </c>
+      <c r="E6" t="s">
         <v>53</v>
       </c>
-      <c r="C6">
-        <v>19</v>
-      </c>
-      <c r="D6">
-        <v>1</v>
-      </c>
-      <c r="E6" t="s">
+      <c r="F6" t="s">
         <v>54</v>
       </c>
-      <c r="F6" t="s">
+      <c r="G6" t="s">
         <v>55</v>
-      </c>
-      <c r="G6" t="s">
-        <v>56</v>
       </c>
       <c r="H6" t="s">
         <v>14</v>
@@ -1370,112 +1547,103 @@
         <v>150</v>
       </c>
       <c r="J6" t="s">
-        <v>185</v>
-      </c>
-      <c r="K6" t="s">
-        <v>15</v>
+        <v>186</v>
       </c>
     </row>
     <row r="7" spans="1:11" x14ac:dyDescent="0.25">
       <c r="A7" t="s">
-        <v>21</v>
+        <v>20</v>
       </c>
       <c r="B7" t="s">
-        <v>19</v>
-      </c>
-      <c r="C7">
-        <v>5</v>
+        <v>18</v>
+      </c>
+      <c r="C7" t="s">
+        <v>184</v>
       </c>
       <c r="D7">
         <v>8</v>
       </c>
       <c r="E7" t="s">
-        <v>36</v>
+        <v>35</v>
       </c>
       <c r="F7" t="s">
+        <v>56</v>
+      </c>
+      <c r="G7" t="s">
         <v>57</v>
       </c>
-      <c r="G7" t="s">
-        <v>58</v>
-      </c>
       <c r="H7" t="s">
-        <v>26</v>
+        <v>25</v>
       </c>
       <c r="I7">
         <v>350</v>
       </c>
       <c r="J7" t="s">
-        <v>186</v>
-      </c>
-      <c r="K7" t="s">
-        <v>15</v>
+        <v>187</v>
       </c>
     </row>
     <row r="8" spans="1:11" x14ac:dyDescent="0.25">
       <c r="A8" t="s">
-        <v>21</v>
+        <v>20</v>
       </c>
       <c r="B8" t="s">
-        <v>19</v>
-      </c>
-      <c r="C8">
-        <v>5</v>
+        <v>18</v>
+      </c>
+      <c r="C8" t="s">
+        <v>184</v>
       </c>
       <c r="D8">
         <v>8</v>
       </c>
       <c r="E8" t="s">
-        <v>36</v>
+        <v>35</v>
       </c>
       <c r="F8" t="s">
-        <v>59</v>
+        <v>58</v>
       </c>
       <c r="G8" t="s">
-        <v>58</v>
+        <v>57</v>
       </c>
       <c r="H8" t="s">
-        <v>26</v>
+        <v>25</v>
       </c>
       <c r="I8">
         <v>350</v>
       </c>
       <c r="J8" t="s">
-        <v>187</v>
-      </c>
-      <c r="K8" t="s">
-        <v>15</v>
+        <v>188</v>
       </c>
     </row>
     <row r="9" spans="1:11" x14ac:dyDescent="0.25">
       <c r="A9" t="s">
-        <v>21</v>
+        <v>20</v>
       </c>
       <c r="B9" t="s">
-        <v>38</v>
-      </c>
-      <c r="C9">
-        <v>19</v>
+        <v>37</v>
+      </c>
+      <c r="C9" t="s">
+        <v>180</v>
       </c>
       <c r="D9">
         <v>1</v>
       </c>
+      <c r="E9" t="s">
+        <v>189</v>
+      </c>
       <c r="F9" t="s">
+        <v>59</v>
+      </c>
+      <c r="G9" t="s">
         <v>60</v>
       </c>
-      <c r="G9" t="s">
-        <v>61</v>
-      </c>
       <c r="H9" t="s">
-        <v>33</v>
+        <v>32</v>
       </c>
       <c r="I9">
         <v>200</v>
       </c>
       <c r="J9" t="s">
-        <v>188</v>
-      </c>
-      <c r="K9" t="s">
-        <v>15</v>
+        <v>190</v>
       </c>
     </row>
     <row r="10" spans="1:11" x14ac:dyDescent="0.25">
@@ -1483,54 +1651,54 @@
         <v>11</v>
       </c>
       <c r="B10" t="s">
-        <v>38</v>
-      </c>
-      <c r="C10">
-        <v>19</v>
+        <v>37</v>
+      </c>
+      <c r="C10" t="s">
+        <v>180</v>
       </c>
       <c r="D10">
         <v>10</v>
       </c>
+      <c r="E10" t="s">
+        <v>189</v>
+      </c>
       <c r="F10" t="s">
-        <v>62</v>
+        <v>61</v>
       </c>
       <c r="G10" t="s">
+        <v>27</v>
+      </c>
+      <c r="H10" t="s">
         <v>28</v>
-      </c>
-      <c r="H10" t="s">
-        <v>29</v>
       </c>
       <c r="I10">
         <v>240</v>
       </c>
       <c r="J10" t="s">
-        <v>189</v>
-      </c>
-      <c r="K10" t="s">
-        <v>15</v>
+        <v>191</v>
       </c>
     </row>
     <row r="11" spans="1:11" x14ac:dyDescent="0.25">
       <c r="A11" t="s">
-        <v>21</v>
+        <v>20</v>
       </c>
       <c r="B11" t="s">
-        <v>16</v>
-      </c>
-      <c r="C11">
-        <v>5</v>
+        <v>15</v>
+      </c>
+      <c r="C11" t="s">
+        <v>184</v>
       </c>
       <c r="D11">
         <v>1</v>
       </c>
       <c r="E11" t="s">
+        <v>62</v>
+      </c>
+      <c r="F11" t="s">
         <v>63</v>
       </c>
-      <c r="F11" t="s">
-        <v>64</v>
-      </c>
       <c r="G11" t="s">
-        <v>37</v>
+        <v>36</v>
       </c>
       <c r="H11" t="s">
         <v>14</v>
@@ -1539,33 +1707,30 @@
         <v>220</v>
       </c>
       <c r="J11" t="s">
-        <v>190</v>
-      </c>
-      <c r="K11" t="s">
-        <v>15</v>
+        <v>192</v>
       </c>
     </row>
     <row r="12" spans="1:11" x14ac:dyDescent="0.25">
       <c r="A12" t="s">
-        <v>21</v>
+        <v>20</v>
       </c>
       <c r="B12" t="s">
-        <v>16</v>
-      </c>
-      <c r="C12">
-        <v>5</v>
+        <v>15</v>
+      </c>
+      <c r="C12" t="s">
+        <v>184</v>
       </c>
       <c r="D12">
         <v>1</v>
       </c>
       <c r="E12" t="s">
+        <v>64</v>
+      </c>
+      <c r="F12" t="s">
         <v>65</v>
       </c>
-      <c r="F12" t="s">
-        <v>66</v>
-      </c>
       <c r="G12" t="s">
-        <v>37</v>
+        <v>36</v>
       </c>
       <c r="H12" t="s">
         <v>14</v>
@@ -1574,33 +1739,30 @@
         <v>220</v>
       </c>
       <c r="J12" t="s">
-        <v>191</v>
-      </c>
-      <c r="K12" t="s">
-        <v>15</v>
+        <v>193</v>
       </c>
     </row>
     <row r="13" spans="1:11" x14ac:dyDescent="0.25">
       <c r="A13" t="s">
-        <v>21</v>
+        <v>20</v>
       </c>
       <c r="B13" t="s">
-        <v>16</v>
-      </c>
-      <c r="C13">
-        <v>5</v>
+        <v>15</v>
+      </c>
+      <c r="C13" t="s">
+        <v>184</v>
       </c>
       <c r="D13">
         <v>1</v>
       </c>
       <c r="E13" t="s">
+        <v>66</v>
+      </c>
+      <c r="F13" t="s">
         <v>67</v>
       </c>
-      <c r="F13" t="s">
-        <v>68</v>
-      </c>
       <c r="G13" t="s">
-        <v>37</v>
+        <v>36</v>
       </c>
       <c r="H13" t="s">
         <v>14</v>
@@ -1609,30 +1771,30 @@
         <v>220</v>
       </c>
       <c r="J13" t="s">
-        <v>192</v>
-      </c>
-      <c r="K13" t="s">
-        <v>15</v>
+        <v>194</v>
       </c>
     </row>
     <row r="14" spans="1:11" x14ac:dyDescent="0.25">
       <c r="A14" t="s">
-        <v>21</v>
+        <v>20</v>
       </c>
       <c r="B14" t="s">
-        <v>69</v>
-      </c>
-      <c r="C14">
-        <v>5</v>
+        <v>68</v>
+      </c>
+      <c r="C14" t="s">
+        <v>184</v>
       </c>
       <c r="D14">
         <v>5</v>
       </c>
+      <c r="E14" t="s">
+        <v>195</v>
+      </c>
       <c r="F14" t="s">
+        <v>69</v>
+      </c>
+      <c r="G14" t="s">
         <v>70</v>
-      </c>
-      <c r="G14" t="s">
-        <v>71</v>
       </c>
       <c r="H14" t="s">
         <v>14</v>
@@ -1641,10 +1803,7 @@
         <v>700</v>
       </c>
       <c r="J14" t="s">
-        <v>193</v>
-      </c>
-      <c r="K14" t="s">
-        <v>15</v>
+        <v>196</v>
       </c>
     </row>
     <row r="15" spans="1:11" x14ac:dyDescent="0.25">
@@ -1652,34 +1811,31 @@
         <v>11</v>
       </c>
       <c r="B15" t="s">
+        <v>71</v>
+      </c>
+      <c r="C15" t="s">
+        <v>184</v>
+      </c>
+      <c r="D15">
+        <v>1</v>
+      </c>
+      <c r="E15" t="s">
         <v>72</v>
       </c>
-      <c r="C15">
-        <v>5</v>
-      </c>
-      <c r="D15">
-        <v>1</v>
-      </c>
-      <c r="E15" t="s">
+      <c r="F15" t="s">
         <v>73</v>
       </c>
-      <c r="F15" t="s">
+      <c r="G15" t="s">
         <v>74</v>
       </c>
-      <c r="G15" t="s">
-        <v>75</v>
-      </c>
       <c r="H15" t="s">
-        <v>26</v>
+        <v>25</v>
       </c>
       <c r="I15">
         <v>360</v>
       </c>
       <c r="J15" t="s">
-        <v>194</v>
-      </c>
-      <c r="K15" t="s">
-        <v>15</v>
+        <v>197</v>
       </c>
     </row>
     <row r="16" spans="1:11" x14ac:dyDescent="0.25">
@@ -1687,83 +1843,86 @@
         <v>11</v>
       </c>
       <c r="B16" t="s">
-        <v>72</v>
-      </c>
-      <c r="C16">
-        <v>5</v>
+        <v>71</v>
+      </c>
+      <c r="C16" t="s">
+        <v>184</v>
       </c>
       <c r="D16">
         <v>1</v>
       </c>
+      <c r="E16" t="s">
+        <v>189</v>
+      </c>
       <c r="F16" t="s">
-        <v>76</v>
+        <v>75</v>
       </c>
       <c r="G16" t="s">
-        <v>75</v>
+        <v>74</v>
       </c>
       <c r="H16" t="s">
-        <v>26</v>
+        <v>25</v>
       </c>
       <c r="I16">
         <v>360</v>
       </c>
       <c r="J16" t="s">
-        <v>195</v>
-      </c>
-      <c r="K16" t="s">
-        <v>15</v>
-      </c>
-    </row>
-    <row r="17" spans="1:11" x14ac:dyDescent="0.25">
+        <v>198</v>
+      </c>
+    </row>
+    <row r="17" spans="1:10" x14ac:dyDescent="0.25">
       <c r="A17" t="s">
-        <v>21</v>
+        <v>20</v>
       </c>
       <c r="B17" t="s">
-        <v>38</v>
-      </c>
-      <c r="C17">
-        <v>19</v>
+        <v>37</v>
+      </c>
+      <c r="C17" t="s">
+        <v>180</v>
       </c>
       <c r="D17">
         <v>1</v>
       </c>
+      <c r="E17" t="s">
+        <v>189</v>
+      </c>
       <c r="F17" t="s">
-        <v>77</v>
+        <v>76</v>
       </c>
       <c r="G17" t="s">
-        <v>61</v>
+        <v>60</v>
       </c>
       <c r="H17" t="s">
-        <v>33</v>
+        <v>32</v>
       </c>
       <c r="I17">
         <v>200</v>
       </c>
       <c r="J17" t="s">
-        <v>196</v>
-      </c>
-      <c r="K17" t="s">
+        <v>199</v>
+      </c>
+    </row>
+    <row r="18" spans="1:10" x14ac:dyDescent="0.25">
+      <c r="A18" t="s">
+        <v>20</v>
+      </c>
+      <c r="B18" t="s">
         <v>15</v>
       </c>
-    </row>
-    <row r="18" spans="1:11" x14ac:dyDescent="0.25">
-      <c r="A18" t="s">
-        <v>21</v>
-      </c>
-      <c r="B18" t="s">
-        <v>16</v>
-      </c>
-      <c r="C18">
-        <v>5</v>
+      <c r="C18" t="s">
+        <v>184</v>
       </c>
       <c r="D18">
         <v>1</v>
       </c>
+      <c r="E18" t="s">
+        <v>189</v>
+      </c>
       <c r="F18" t="s">
-        <v>78</v>
+        <v>77</v>
       </c>
       <c r="G18" t="s">
-        <v>37</v>
+        <v>36</v>
       </c>
       <c r="H18" t="s">
         <v>14</v>
@@ -1772,30 +1931,27 @@
         <v>2300</v>
       </c>
       <c r="J18" t="s">
-        <v>197</v>
-      </c>
-      <c r="K18" t="s">
-        <v>15</v>
-      </c>
-    </row>
-    <row r="19" spans="1:11" x14ac:dyDescent="0.25">
+        <v>200</v>
+      </c>
+    </row>
+    <row r="19" spans="1:10" x14ac:dyDescent="0.25">
       <c r="A19" t="s">
         <v>11</v>
       </c>
       <c r="B19" t="s">
-        <v>19</v>
-      </c>
-      <c r="C19">
-        <v>19</v>
+        <v>18</v>
+      </c>
+      <c r="C19" t="s">
+        <v>180</v>
       </c>
       <c r="D19">
         <v>1</v>
       </c>
       <c r="E19" t="s">
+        <v>78</v>
+      </c>
+      <c r="F19" t="s">
         <v>79</v>
-      </c>
-      <c r="F19" t="s">
-        <v>80</v>
       </c>
       <c r="G19" t="s">
         <v>13</v>
@@ -1807,100 +1963,94 @@
         <v>240</v>
       </c>
       <c r="J19" t="s">
-        <v>198</v>
-      </c>
-      <c r="K19" t="s">
-        <v>15</v>
-      </c>
-    </row>
-    <row r="20" spans="1:11" x14ac:dyDescent="0.25">
+        <v>201</v>
+      </c>
+    </row>
+    <row r="20" spans="1:10" x14ac:dyDescent="0.25">
       <c r="A20" t="s">
-        <v>21</v>
+        <v>20</v>
       </c>
       <c r="B20" t="s">
-        <v>27</v>
-      </c>
-      <c r="C20">
-        <v>19</v>
+        <v>26</v>
+      </c>
+      <c r="C20" t="s">
+        <v>180</v>
       </c>
       <c r="D20">
         <v>6</v>
       </c>
       <c r="E20" t="s">
-        <v>81</v>
+        <v>80</v>
       </c>
       <c r="F20" t="s">
-        <v>48</v>
+        <v>47</v>
       </c>
       <c r="G20" t="s">
+        <v>27</v>
+      </c>
+      <c r="H20" t="s">
         <v>28</v>
-      </c>
-      <c r="H20" t="s">
-        <v>29</v>
       </c>
       <c r="I20">
         <v>1700</v>
       </c>
       <c r="J20" t="s">
-        <v>199</v>
-      </c>
-      <c r="K20" t="s">
-        <v>15</v>
-      </c>
-    </row>
-    <row r="21" spans="1:11" x14ac:dyDescent="0.25">
+        <v>202</v>
+      </c>
+    </row>
+    <row r="21" spans="1:10" x14ac:dyDescent="0.25">
       <c r="A21" t="s">
-        <v>21</v>
+        <v>20</v>
       </c>
       <c r="B21" t="s">
+        <v>81</v>
+      </c>
+      <c r="C21" t="s">
+        <v>184</v>
+      </c>
+      <c r="D21">
+        <v>1</v>
+      </c>
+      <c r="E21" t="s">
         <v>82</v>
       </c>
-      <c r="C21">
-        <v>5</v>
-      </c>
-      <c r="D21">
-        <v>1</v>
-      </c>
-      <c r="E21" t="s">
+      <c r="F21" t="s">
         <v>83</v>
       </c>
-      <c r="F21" t="s">
+      <c r="G21" t="s">
         <v>84</v>
       </c>
-      <c r="G21" t="s">
-        <v>85</v>
-      </c>
       <c r="H21" t="s">
-        <v>17</v>
+        <v>16</v>
       </c>
       <c r="I21">
         <v>260</v>
       </c>
       <c r="J21" t="s">
-        <v>200</v>
-      </c>
-      <c r="K21" t="s">
-        <v>15</v>
-      </c>
-    </row>
-    <row r="22" spans="1:11" x14ac:dyDescent="0.25">
+        <v>203</v>
+      </c>
+    </row>
+    <row r="22" spans="1:10" x14ac:dyDescent="0.25">
       <c r="A22" t="s">
-        <v>21</v>
+        <v>20</v>
       </c>
       <c r="B22" t="s">
-        <v>86</v>
-      </c>
-      <c r="C22">
-        <v>19</v>
+        <v>85</v>
+      </c>
+      <c r="C22" t="s">
+        <v>180</v>
       </c>
       <c r="D22">
         <v>50</v>
       </c>
+      <c r="E22" t="s">
+        <v>189</v>
+      </c>
       <c r="F22" t="s">
+        <v>86</v>
+      </c>
+      <c r="G22" t="s">
         <v>87</v>
-      </c>
-      <c r="G22" t="s">
-        <v>88</v>
       </c>
       <c r="H22" t="s">
         <v>14</v>
@@ -1909,30 +2059,30 @@
         <v>400</v>
       </c>
       <c r="J22" t="s">
-        <v>201</v>
-      </c>
-      <c r="K22" t="s">
-        <v>15</v>
-      </c>
-    </row>
-    <row r="23" spans="1:11" x14ac:dyDescent="0.25">
+        <v>204</v>
+      </c>
+    </row>
+    <row r="23" spans="1:10" x14ac:dyDescent="0.25">
       <c r="A23" t="s">
-        <v>21</v>
+        <v>20</v>
       </c>
       <c r="B23" t="s">
-        <v>86</v>
-      </c>
-      <c r="C23">
-        <v>19</v>
+        <v>85</v>
+      </c>
+      <c r="C23" t="s">
+        <v>180</v>
       </c>
       <c r="D23">
         <v>50</v>
       </c>
+      <c r="E23" t="s">
+        <v>189</v>
+      </c>
       <c r="F23" t="s">
-        <v>89</v>
+        <v>88</v>
       </c>
       <c r="G23" t="s">
-        <v>88</v>
+        <v>87</v>
       </c>
       <c r="H23" t="s">
         <v>14</v>
@@ -1941,103 +2091,94 @@
         <v>400</v>
       </c>
       <c r="J23" t="s">
-        <v>202</v>
-      </c>
-      <c r="K23" t="s">
-        <v>15</v>
-      </c>
-    </row>
-    <row r="24" spans="1:11" x14ac:dyDescent="0.25">
+        <v>205</v>
+      </c>
+    </row>
+    <row r="24" spans="1:10" x14ac:dyDescent="0.25">
       <c r="A24" t="s">
         <v>11</v>
       </c>
       <c r="B24" t="s">
+        <v>18</v>
+      </c>
+      <c r="C24" t="s">
+        <v>184</v>
+      </c>
+      <c r="D24">
+        <v>1</v>
+      </c>
+      <c r="E24" t="s">
+        <v>89</v>
+      </c>
+      <c r="F24" t="s">
+        <v>90</v>
+      </c>
+      <c r="G24" t="s">
         <v>19</v>
       </c>
-      <c r="C24">
-        <v>5</v>
-      </c>
-      <c r="D24">
-        <v>1</v>
-      </c>
-      <c r="E24" t="s">
-        <v>90</v>
-      </c>
-      <c r="F24" t="s">
-        <v>91</v>
-      </c>
-      <c r="G24" t="s">
-        <v>20</v>
-      </c>
       <c r="H24" t="s">
-        <v>26</v>
+        <v>25</v>
       </c>
       <c r="I24">
         <v>240</v>
       </c>
       <c r="J24" t="s">
-        <v>203</v>
-      </c>
-      <c r="K24" t="s">
-        <v>15</v>
-      </c>
-    </row>
-    <row r="25" spans="1:11" x14ac:dyDescent="0.25">
+        <v>206</v>
+      </c>
+    </row>
+    <row r="25" spans="1:10" x14ac:dyDescent="0.25">
       <c r="A25" t="s">
-        <v>21</v>
+        <v>20</v>
       </c>
       <c r="B25" t="s">
-        <v>27</v>
-      </c>
-      <c r="C25">
-        <v>19</v>
+        <v>26</v>
+      </c>
+      <c r="C25" t="s">
+        <v>180</v>
       </c>
       <c r="D25">
         <v>2</v>
       </c>
       <c r="E25" t="s">
-        <v>30</v>
+        <v>29</v>
       </c>
       <c r="F25" t="s">
-        <v>48</v>
+        <v>47</v>
       </c>
       <c r="G25" t="s">
+        <v>27</v>
+      </c>
+      <c r="H25" t="s">
         <v>28</v>
-      </c>
-      <c r="H25" t="s">
-        <v>29</v>
       </c>
       <c r="I25">
         <v>600</v>
       </c>
       <c r="J25" t="s">
-        <v>204</v>
-      </c>
-      <c r="K25" t="s">
-        <v>15</v>
-      </c>
-    </row>
-    <row r="26" spans="1:11" x14ac:dyDescent="0.25">
+        <v>207</v>
+      </c>
+    </row>
+    <row r="26" spans="1:10" x14ac:dyDescent="0.25">
       <c r="A26" t="s">
-        <v>21</v>
+        <v>20</v>
       </c>
       <c r="B26" t="s">
-        <v>53</v>
-      </c>
-      <c r="C26">
-        <v>19</v>
+        <v>52</v>
+      </c>
+      <c r="C26" t="s">
+        <v>180</v>
       </c>
       <c r="D26">
         <v>10</v>
       </c>
       <c r="E26" t="s">
+        <v>53</v>
+      </c>
+      <c r="F26" t="s">
         <v>54</v>
       </c>
-      <c r="F26" t="s">
+      <c r="G26" t="s">
         <v>55</v>
-      </c>
-      <c r="G26" t="s">
-        <v>56</v>
       </c>
       <c r="H26" t="s">
         <v>14</v>
@@ -2046,272 +2187,254 @@
         <v>300</v>
       </c>
       <c r="J26" t="s">
-        <v>205</v>
-      </c>
-      <c r="K26" t="s">
-        <v>15</v>
-      </c>
-    </row>
-    <row r="27" spans="1:11" x14ac:dyDescent="0.25">
+        <v>208</v>
+      </c>
+    </row>
+    <row r="27" spans="1:10" x14ac:dyDescent="0.25">
       <c r="A27" t="s">
         <v>11</v>
       </c>
       <c r="B27" t="s">
-        <v>18</v>
-      </c>
-      <c r="C27">
-        <v>19</v>
+        <v>17</v>
+      </c>
+      <c r="C27" t="s">
+        <v>180</v>
       </c>
       <c r="D27">
         <v>1</v>
       </c>
       <c r="E27" t="s">
+        <v>91</v>
+      </c>
+      <c r="F27" t="s">
         <v>92</v>
       </c>
-      <c r="F27" t="s">
-        <v>93</v>
-      </c>
       <c r="G27" t="s">
-        <v>23</v>
+        <v>22</v>
       </c>
       <c r="H27" t="s">
-        <v>26</v>
+        <v>25</v>
       </c>
       <c r="I27">
         <v>240</v>
       </c>
       <c r="J27" t="s">
-        <v>206</v>
-      </c>
-      <c r="K27" t="s">
-        <v>15</v>
-      </c>
-    </row>
-    <row r="28" spans="1:11" x14ac:dyDescent="0.25">
+        <v>209</v>
+      </c>
+    </row>
+    <row r="28" spans="1:10" x14ac:dyDescent="0.25">
       <c r="A28" t="s">
         <v>11</v>
       </c>
       <c r="B28" t="s">
-        <v>18</v>
-      </c>
-      <c r="C28">
-        <v>19</v>
+        <v>17</v>
+      </c>
+      <c r="C28" t="s">
+        <v>180</v>
       </c>
       <c r="D28">
         <v>1</v>
       </c>
       <c r="E28" t="s">
-        <v>94</v>
+        <v>93</v>
       </c>
       <c r="F28" t="s">
-        <v>94</v>
+        <v>93</v>
       </c>
       <c r="G28" t="s">
-        <v>23</v>
+        <v>22</v>
       </c>
       <c r="H28" t="s">
-        <v>26</v>
+        <v>25</v>
       </c>
       <c r="I28">
         <v>300</v>
       </c>
       <c r="J28" t="s">
-        <v>207</v>
-      </c>
-      <c r="K28" t="s">
-        <v>15</v>
-      </c>
-    </row>
-    <row r="29" spans="1:11" x14ac:dyDescent="0.25">
+        <v>210</v>
+      </c>
+    </row>
+    <row r="29" spans="1:10" x14ac:dyDescent="0.25">
       <c r="A29" t="s">
-        <v>21</v>
+        <v>20</v>
       </c>
       <c r="B29" t="s">
-        <v>53</v>
-      </c>
-      <c r="C29">
-        <v>19</v>
+        <v>52</v>
+      </c>
+      <c r="C29" t="s">
+        <v>180</v>
       </c>
       <c r="D29">
         <v>4</v>
       </c>
+      <c r="E29" t="s">
+        <v>211</v>
+      </c>
       <c r="F29" t="s">
+        <v>94</v>
+      </c>
+      <c r="G29" t="s">
         <v>95</v>
       </c>
-      <c r="G29" t="s">
+      <c r="H29" t="s">
         <v>96</v>
-      </c>
-      <c r="H29" t="s">
-        <v>97</v>
       </c>
       <c r="I29">
         <v>350</v>
       </c>
       <c r="J29" t="s">
-        <v>208</v>
-      </c>
-      <c r="K29" t="s">
-        <v>15</v>
-      </c>
-    </row>
-    <row r="30" spans="1:11" x14ac:dyDescent="0.25">
+        <v>212</v>
+      </c>
+    </row>
+    <row r="30" spans="1:10" x14ac:dyDescent="0.25">
       <c r="A30" t="s">
         <v>11</v>
       </c>
       <c r="B30" t="s">
+        <v>97</v>
+      </c>
+      <c r="C30" t="s">
+        <v>184</v>
+      </c>
+      <c r="D30">
+        <v>1</v>
+      </c>
+      <c r="E30" t="s">
+        <v>189</v>
+      </c>
+      <c r="F30" t="s">
         <v>98</v>
       </c>
-      <c r="C30">
-        <v>5</v>
-      </c>
-      <c r="D30">
-        <v>1</v>
-      </c>
-      <c r="F30" t="s">
+      <c r="G30" t="s">
         <v>99</v>
       </c>
-      <c r="G30" t="s">
+      <c r="H30" t="s">
         <v>100</v>
-      </c>
-      <c r="H30" t="s">
-        <v>101</v>
       </c>
       <c r="I30">
         <v>480</v>
       </c>
       <c r="J30" t="s">
-        <v>209</v>
-      </c>
-      <c r="K30" t="s">
-        <v>15</v>
-      </c>
-    </row>
-    <row r="31" spans="1:11" x14ac:dyDescent="0.25">
+        <v>213</v>
+      </c>
+    </row>
+    <row r="31" spans="1:10" x14ac:dyDescent="0.25">
       <c r="A31" t="s">
         <v>11</v>
       </c>
       <c r="B31" t="s">
         <v>12</v>
       </c>
-      <c r="C31">
-        <v>3</v>
+      <c r="C31" t="s">
+        <v>214</v>
       </c>
       <c r="D31">
         <v>1</v>
       </c>
       <c r="E31" t="s">
+        <v>103</v>
+      </c>
+      <c r="F31" t="s">
         <v>104</v>
       </c>
-      <c r="F31" t="s">
-        <v>105</v>
-      </c>
       <c r="G31" t="s">
-        <v>46</v>
+        <v>45</v>
       </c>
       <c r="H31" t="s">
-        <v>26</v>
+        <v>25</v>
       </c>
       <c r="I31">
         <v>360</v>
       </c>
       <c r="J31" t="s">
-        <v>210</v>
-      </c>
-      <c r="K31" t="s">
-        <v>15</v>
-      </c>
-    </row>
-    <row r="32" spans="1:11" x14ac:dyDescent="0.25">
+        <v>215</v>
+      </c>
+    </row>
+    <row r="32" spans="1:10" x14ac:dyDescent="0.25">
       <c r="A32" t="s">
-        <v>21</v>
+        <v>20</v>
       </c>
       <c r="B32" t="s">
+        <v>101</v>
+      </c>
+      <c r="C32" t="s">
+        <v>214</v>
+      </c>
+      <c r="D32">
+        <v>1</v>
+      </c>
+      <c r="E32" t="s">
+        <v>105</v>
+      </c>
+      <c r="F32" t="s">
+        <v>106</v>
+      </c>
+      <c r="G32" t="s">
         <v>102</v>
       </c>
-      <c r="C32">
-        <v>3</v>
-      </c>
-      <c r="D32">
-        <v>1</v>
-      </c>
-      <c r="E32" t="s">
-        <v>106</v>
-      </c>
-      <c r="F32" t="s">
-        <v>107</v>
-      </c>
-      <c r="G32" t="s">
-        <v>103</v>
-      </c>
       <c r="H32" t="s">
-        <v>101</v>
+        <v>100</v>
       </c>
       <c r="I32">
         <v>600</v>
       </c>
       <c r="J32" t="s">
-        <v>211</v>
-      </c>
-      <c r="K32" t="s">
-        <v>15</v>
-      </c>
-    </row>
-    <row r="33" spans="1:11" x14ac:dyDescent="0.25">
+        <v>216</v>
+      </c>
+    </row>
+    <row r="33" spans="1:10" x14ac:dyDescent="0.25">
       <c r="A33" t="s">
-        <v>21</v>
+        <v>20</v>
       </c>
       <c r="B33" t="s">
-        <v>34</v>
-      </c>
-      <c r="C33">
-        <v>5</v>
+        <v>33</v>
+      </c>
+      <c r="C33" t="s">
+        <v>184</v>
       </c>
       <c r="D33">
         <v>1</v>
       </c>
       <c r="E33" t="s">
+        <v>107</v>
+      </c>
+      <c r="F33" t="s">
         <v>108</v>
       </c>
-      <c r="F33" t="s">
+      <c r="G33" t="s">
         <v>109</v>
       </c>
-      <c r="G33" t="s">
-        <v>110</v>
-      </c>
       <c r="H33" t="s">
-        <v>24</v>
+        <v>23</v>
       </c>
       <c r="I33">
         <v>700</v>
       </c>
       <c r="J33" t="s">
-        <v>212</v>
-      </c>
-      <c r="K33" t="s">
-        <v>15</v>
-      </c>
-    </row>
-    <row r="34" spans="1:11" x14ac:dyDescent="0.25">
+        <v>217</v>
+      </c>
+    </row>
+    <row r="34" spans="1:10" x14ac:dyDescent="0.25">
       <c r="A34" t="s">
-        <v>21</v>
+        <v>20</v>
       </c>
       <c r="B34" t="s">
-        <v>111</v>
-      </c>
-      <c r="C34">
-        <v>5</v>
+        <v>110</v>
+      </c>
+      <c r="C34" t="s">
+        <v>184</v>
       </c>
       <c r="D34">
         <v>5</v>
       </c>
       <c r="E34" t="s">
-        <v>39</v>
+        <v>38</v>
       </c>
       <c r="F34" t="s">
+        <v>111</v>
+      </c>
+      <c r="G34" t="s">
         <v>112</v>
-      </c>
-      <c r="G34" t="s">
-        <v>113</v>
       </c>
       <c r="H34" t="s">
         <v>14</v>
@@ -2320,167 +2443,158 @@
         <v>1200</v>
       </c>
       <c r="J34" t="s">
-        <v>213</v>
-      </c>
-      <c r="K34" t="s">
-        <v>15</v>
-      </c>
-    </row>
-    <row r="35" spans="1:11" x14ac:dyDescent="0.25">
+        <v>218</v>
+      </c>
+    </row>
+    <row r="35" spans="1:10" x14ac:dyDescent="0.25">
       <c r="A35" t="s">
-        <v>21</v>
+        <v>20</v>
       </c>
       <c r="B35" t="s">
-        <v>114</v>
-      </c>
-      <c r="C35">
-        <v>5</v>
+        <v>113</v>
+      </c>
+      <c r="C35" t="s">
+        <v>184</v>
       </c>
       <c r="D35">
         <v>2</v>
       </c>
       <c r="E35" t="s">
-        <v>22</v>
+        <v>21</v>
       </c>
       <c r="F35" t="s">
-        <v>115</v>
+        <v>114</v>
       </c>
       <c r="G35" t="s">
-        <v>20</v>
+        <v>19</v>
       </c>
       <c r="H35" t="s">
-        <v>26</v>
+        <v>25</v>
       </c>
       <c r="I35">
         <v>850</v>
       </c>
       <c r="J35" t="s">
-        <v>214</v>
-      </c>
-      <c r="K35" t="s">
-        <v>15</v>
-      </c>
-    </row>
-    <row r="36" spans="1:11" x14ac:dyDescent="0.25">
+        <v>219</v>
+      </c>
+    </row>
+    <row r="36" spans="1:10" x14ac:dyDescent="0.25">
       <c r="A36" t="s">
-        <v>21</v>
+        <v>20</v>
       </c>
       <c r="B36" t="s">
-        <v>116</v>
-      </c>
-      <c r="C36">
-        <v>19</v>
+        <v>115</v>
+      </c>
+      <c r="C36" t="s">
+        <v>180</v>
       </c>
       <c r="D36">
         <v>2</v>
       </c>
+      <c r="E36" t="s">
+        <v>195</v>
+      </c>
       <c r="F36" t="s">
+        <v>116</v>
+      </c>
+      <c r="G36" t="s">
         <v>117</v>
       </c>
-      <c r="G36" t="s">
-        <v>118</v>
-      </c>
       <c r="H36" t="s">
-        <v>29</v>
+        <v>28</v>
       </c>
       <c r="I36">
         <v>450</v>
       </c>
       <c r="J36" t="s">
-        <v>215</v>
-      </c>
-      <c r="K36" t="s">
-        <v>15</v>
-      </c>
-    </row>
-    <row r="37" spans="1:11" x14ac:dyDescent="0.25">
+        <v>220</v>
+      </c>
+    </row>
+    <row r="37" spans="1:10" x14ac:dyDescent="0.25">
       <c r="A37" t="s">
-        <v>21</v>
+        <v>20</v>
       </c>
       <c r="B37" t="s">
-        <v>27</v>
-      </c>
-      <c r="C37">
-        <v>19</v>
+        <v>26</v>
+      </c>
+      <c r="C37" t="s">
+        <v>180</v>
       </c>
       <c r="D37">
         <v>6</v>
       </c>
       <c r="E37" t="s">
-        <v>81</v>
+        <v>80</v>
       </c>
       <c r="F37" t="s">
-        <v>48</v>
+        <v>47</v>
       </c>
       <c r="G37" t="s">
+        <v>27</v>
+      </c>
+      <c r="H37" t="s">
         <v>28</v>
-      </c>
-      <c r="H37" t="s">
-        <v>29</v>
       </c>
       <c r="I37">
         <v>1700</v>
       </c>
       <c r="J37" t="s">
-        <v>216</v>
-      </c>
-      <c r="K37" t="s">
-        <v>15</v>
-      </c>
-    </row>
-    <row r="38" spans="1:11" x14ac:dyDescent="0.25">
+        <v>221</v>
+      </c>
+    </row>
+    <row r="38" spans="1:10" x14ac:dyDescent="0.25">
       <c r="A38" t="s">
-        <v>21</v>
+        <v>20</v>
       </c>
       <c r="B38" t="s">
-        <v>27</v>
-      </c>
-      <c r="C38">
-        <v>19</v>
+        <v>26</v>
+      </c>
+      <c r="C38" t="s">
+        <v>180</v>
       </c>
       <c r="D38">
         <v>2</v>
       </c>
       <c r="E38" t="s">
-        <v>31</v>
+        <v>30</v>
       </c>
       <c r="F38" t="s">
-        <v>48</v>
+        <v>47</v>
       </c>
       <c r="G38" t="s">
+        <v>27</v>
+      </c>
+      <c r="H38" t="s">
         <v>28</v>
-      </c>
-      <c r="H38" t="s">
-        <v>29</v>
       </c>
       <c r="I38">
         <v>600</v>
       </c>
       <c r="J38" t="s">
-        <v>217</v>
-      </c>
-      <c r="K38" t="s">
-        <v>15</v>
-      </c>
-    </row>
-    <row r="39" spans="1:11" x14ac:dyDescent="0.25">
+        <v>222</v>
+      </c>
+    </row>
+    <row r="39" spans="1:10" x14ac:dyDescent="0.25">
       <c r="A39" t="s">
-        <v>21</v>
+        <v>20</v>
       </c>
       <c r="B39" t="s">
-        <v>69</v>
-      </c>
-      <c r="C39">
-        <v>5</v>
+        <v>68</v>
+      </c>
+      <c r="C39" t="s">
+        <v>184</v>
       </c>
       <c r="D39">
         <v>1</v>
       </c>
+      <c r="E39" t="s">
+        <v>195</v>
+      </c>
       <c r="F39" t="s">
-        <v>119</v>
+        <v>118</v>
       </c>
       <c r="G39" t="s">
-        <v>71</v>
+        <v>70</v>
       </c>
       <c r="H39" t="s">
         <v>14</v>
@@ -2489,583 +2603,574 @@
         <v>450</v>
       </c>
       <c r="J39" t="s">
-        <v>218</v>
-      </c>
-      <c r="K39" t="s">
-        <v>15</v>
-      </c>
-    </row>
-    <row r="40" spans="1:11" x14ac:dyDescent="0.25">
+        <v>223</v>
+      </c>
+    </row>
+    <row r="40" spans="1:10" x14ac:dyDescent="0.25">
       <c r="A40" t="s">
-        <v>21</v>
+        <v>20</v>
       </c>
       <c r="B40" t="s">
-        <v>120</v>
-      </c>
-      <c r="C40">
-        <v>3</v>
+        <v>119</v>
+      </c>
+      <c r="C40" t="s">
+        <v>214</v>
       </c>
       <c r="D40">
         <v>2</v>
       </c>
+      <c r="E40" t="s">
+        <v>189</v>
+      </c>
       <c r="F40" t="s">
+        <v>120</v>
+      </c>
+      <c r="G40" t="s">
         <v>121</v>
       </c>
-      <c r="G40" t="s">
+      <c r="H40" t="s">
         <v>122</v>
-      </c>
-      <c r="H40" t="s">
-        <v>123</v>
       </c>
       <c r="I40">
         <v>100</v>
       </c>
       <c r="J40" t="s">
-        <v>219</v>
-      </c>
-      <c r="K40" t="s">
-        <v>15</v>
-      </c>
-    </row>
-    <row r="41" spans="1:11" x14ac:dyDescent="0.25">
+        <v>224</v>
+      </c>
+    </row>
+    <row r="41" spans="1:10" x14ac:dyDescent="0.25">
       <c r="A41" t="s">
-        <v>21</v>
+        <v>20</v>
       </c>
       <c r="B41" t="s">
-        <v>120</v>
-      </c>
-      <c r="C41">
-        <v>3</v>
+        <v>119</v>
+      </c>
+      <c r="C41" t="s">
+        <v>214</v>
       </c>
       <c r="D41">
         <v>2</v>
       </c>
+      <c r="E41" t="s">
+        <v>189</v>
+      </c>
       <c r="F41" t="s">
-        <v>124</v>
+        <v>123</v>
       </c>
       <c r="G41" t="s">
+        <v>121</v>
+      </c>
+      <c r="H41" t="s">
         <v>122</v>
-      </c>
-      <c r="H41" t="s">
-        <v>123</v>
       </c>
       <c r="I41">
         <v>100</v>
       </c>
       <c r="J41" t="s">
-        <v>220</v>
-      </c>
-      <c r="K41" t="s">
-        <v>15</v>
-      </c>
-    </row>
-    <row r="42" spans="1:11" x14ac:dyDescent="0.25">
+        <v>225</v>
+      </c>
+    </row>
+    <row r="42" spans="1:10" x14ac:dyDescent="0.25">
       <c r="A42" t="s">
-        <v>21</v>
+        <v>20</v>
       </c>
       <c r="B42" t="s">
-        <v>120</v>
-      </c>
-      <c r="C42">
-        <v>3</v>
+        <v>119</v>
+      </c>
+      <c r="C42" t="s">
+        <v>214</v>
       </c>
       <c r="D42">
         <v>2</v>
       </c>
+      <c r="E42" t="s">
+        <v>189</v>
+      </c>
       <c r="F42" t="s">
-        <v>125</v>
+        <v>124</v>
       </c>
       <c r="G42" t="s">
+        <v>121</v>
+      </c>
+      <c r="H42" t="s">
         <v>122</v>
-      </c>
-      <c r="H42" t="s">
-        <v>123</v>
       </c>
       <c r="I42">
         <v>250</v>
       </c>
       <c r="J42" t="s">
-        <v>221</v>
-      </c>
-      <c r="K42" t="s">
-        <v>15</v>
-      </c>
-    </row>
-    <row r="43" spans="1:11" x14ac:dyDescent="0.25">
+        <v>226</v>
+      </c>
+    </row>
+    <row r="43" spans="1:10" x14ac:dyDescent="0.25">
       <c r="A43" t="s">
-        <v>21</v>
+        <v>20</v>
       </c>
       <c r="B43" t="s">
+        <v>125</v>
+      </c>
+      <c r="C43" t="s">
+        <v>184</v>
+      </c>
+      <c r="D43">
+        <v>1</v>
+      </c>
+      <c r="E43" t="s">
+        <v>195</v>
+      </c>
+      <c r="F43" t="s">
         <v>126</v>
       </c>
-      <c r="C43">
-        <v>5</v>
-      </c>
-      <c r="D43">
-        <v>1</v>
-      </c>
-      <c r="F43" t="s">
-        <v>127</v>
-      </c>
       <c r="G43" t="s">
-        <v>85</v>
+        <v>84</v>
       </c>
       <c r="H43" t="s">
-        <v>17</v>
+        <v>16</v>
       </c>
       <c r="I43">
         <v>350</v>
       </c>
       <c r="J43" t="s">
-        <v>222</v>
-      </c>
-      <c r="K43" t="s">
-        <v>15</v>
-      </c>
-    </row>
-    <row r="44" spans="1:11" x14ac:dyDescent="0.25">
+        <v>227</v>
+      </c>
+    </row>
+    <row r="44" spans="1:10" x14ac:dyDescent="0.25">
       <c r="A44" t="s">
         <v>11</v>
       </c>
       <c r="B44" t="s">
+        <v>127</v>
+      </c>
+      <c r="C44" t="s">
+        <v>180</v>
+      </c>
+      <c r="D44">
+        <v>1</v>
+      </c>
+      <c r="E44" t="s">
+        <v>189</v>
+      </c>
+      <c r="F44" t="s">
         <v>128</v>
       </c>
-      <c r="C44">
-        <v>19</v>
-      </c>
-      <c r="D44">
-        <v>1</v>
-      </c>
-      <c r="F44" t="s">
+      <c r="G44" t="s">
         <v>129</v>
       </c>
-      <c r="G44" t="s">
-        <v>130</v>
-      </c>
       <c r="H44" t="s">
-        <v>35</v>
+        <v>34</v>
       </c>
       <c r="I44">
         <v>480</v>
       </c>
       <c r="J44" t="s">
-        <v>223</v>
-      </c>
-      <c r="K44" t="s">
-        <v>15</v>
-      </c>
-    </row>
-    <row r="45" spans="1:11" x14ac:dyDescent="0.25">
+        <v>228</v>
+      </c>
+    </row>
+    <row r="45" spans="1:10" x14ac:dyDescent="0.25">
       <c r="A45" t="s">
         <v>11</v>
       </c>
       <c r="B45" t="s">
-        <v>128</v>
-      </c>
-      <c r="C45">
-        <v>19</v>
+        <v>127</v>
+      </c>
+      <c r="C45" t="s">
+        <v>180</v>
       </c>
       <c r="D45">
         <v>1</v>
       </c>
+      <c r="E45" t="s">
+        <v>189</v>
+      </c>
       <c r="F45" t="s">
-        <v>131</v>
+        <v>130</v>
       </c>
       <c r="G45" t="s">
-        <v>130</v>
+        <v>129</v>
       </c>
       <c r="H45" t="s">
-        <v>35</v>
+        <v>34</v>
       </c>
       <c r="I45">
         <v>480</v>
       </c>
       <c r="J45" t="s">
-        <v>224</v>
-      </c>
-      <c r="K45" t="s">
-        <v>15</v>
-      </c>
-    </row>
-    <row r="46" spans="1:11" x14ac:dyDescent="0.25">
+        <v>229</v>
+      </c>
+    </row>
+    <row r="46" spans="1:10" x14ac:dyDescent="0.25">
       <c r="A46" t="s">
-        <v>21</v>
+        <v>20</v>
       </c>
       <c r="B46" t="s">
+        <v>131</v>
+      </c>
+      <c r="C46" t="s">
+        <v>184</v>
+      </c>
+      <c r="D46">
+        <v>1</v>
+      </c>
+      <c r="E46" t="s">
+        <v>195</v>
+      </c>
+      <c r="F46" t="s">
         <v>132</v>
       </c>
-      <c r="C46">
-        <v>5</v>
-      </c>
-      <c r="D46">
-        <v>1</v>
-      </c>
-      <c r="F46" t="s">
-        <v>133</v>
-      </c>
       <c r="G46" t="s">
+        <v>31</v>
+      </c>
+      <c r="H46" t="s">
         <v>32</v>
-      </c>
-      <c r="H46" t="s">
-        <v>33</v>
       </c>
       <c r="I46">
         <v>300</v>
       </c>
       <c r="J46" t="s">
-        <v>225</v>
-      </c>
-      <c r="K46" t="s">
-        <v>15</v>
-      </c>
-    </row>
-    <row r="47" spans="1:11" x14ac:dyDescent="0.25">
+        <v>230</v>
+      </c>
+    </row>
+    <row r="47" spans="1:10" x14ac:dyDescent="0.25">
       <c r="A47" t="s">
-        <v>21</v>
+        <v>20</v>
       </c>
       <c r="B47" t="s">
-        <v>134</v>
-      </c>
-      <c r="C47">
-        <v>12</v>
+        <v>133</v>
+      </c>
+      <c r="C47" t="s">
+        <v>231</v>
       </c>
       <c r="D47">
         <v>238</v>
       </c>
+      <c r="E47" t="s">
+        <v>189</v>
+      </c>
       <c r="F47" t="s">
+        <v>134</v>
+      </c>
+      <c r="G47" t="s">
         <v>135</v>
       </c>
-      <c r="G47" t="s">
-        <v>136</v>
-      </c>
       <c r="H47" t="s">
-        <v>24</v>
+        <v>23</v>
       </c>
       <c r="I47">
         <v>850</v>
       </c>
       <c r="J47" t="s">
-        <v>226</v>
-      </c>
-      <c r="K47" t="s">
-        <v>15</v>
-      </c>
-    </row>
-    <row r="48" spans="1:11" x14ac:dyDescent="0.25">
+        <v>232</v>
+      </c>
+    </row>
+    <row r="48" spans="1:10" x14ac:dyDescent="0.25">
       <c r="A48" t="s">
-        <v>21</v>
+        <v>20</v>
       </c>
       <c r="B48" t="s">
-        <v>98</v>
-      </c>
-      <c r="C48">
-        <v>5</v>
+        <v>97</v>
+      </c>
+      <c r="C48" t="s">
+        <v>184</v>
       </c>
       <c r="D48">
         <v>10</v>
       </c>
+      <c r="E48" t="s">
+        <v>189</v>
+      </c>
       <c r="F48" t="s">
-        <v>137</v>
+        <v>136</v>
       </c>
       <c r="G48" t="s">
+        <v>99</v>
+      </c>
+      <c r="H48" t="s">
         <v>100</v>
-      </c>
-      <c r="H48" t="s">
-        <v>101</v>
       </c>
       <c r="I48">
         <v>950</v>
       </c>
       <c r="J48" t="s">
-        <v>227</v>
-      </c>
-      <c r="K48" t="s">
-        <v>15</v>
-      </c>
-    </row>
-    <row r="49" spans="1:11" x14ac:dyDescent="0.25">
+        <v>233</v>
+      </c>
+    </row>
+    <row r="49" spans="1:10" x14ac:dyDescent="0.25">
       <c r="A49" t="s">
-        <v>21</v>
+        <v>20</v>
       </c>
       <c r="B49" t="s">
-        <v>116</v>
-      </c>
-      <c r="C49">
-        <v>19</v>
+        <v>115</v>
+      </c>
+      <c r="C49" t="s">
+        <v>180</v>
       </c>
       <c r="D49">
         <v>4</v>
       </c>
+      <c r="E49" t="s">
+        <v>195</v>
+      </c>
       <c r="F49" t="s">
-        <v>138</v>
+        <v>137</v>
       </c>
       <c r="G49" t="s">
-        <v>118</v>
+        <v>117</v>
       </c>
       <c r="H49" t="s">
-        <v>29</v>
+        <v>28</v>
       </c>
       <c r="I49">
         <v>600</v>
       </c>
       <c r="J49" t="s">
-        <v>228</v>
-      </c>
-      <c r="K49" t="s">
-        <v>15</v>
-      </c>
-    </row>
-    <row r="50" spans="1:11" x14ac:dyDescent="0.25">
+        <v>234</v>
+      </c>
+    </row>
+    <row r="50" spans="1:10" x14ac:dyDescent="0.25">
       <c r="A50" t="s">
         <v>11</v>
       </c>
       <c r="B50" t="s">
-        <v>40</v>
-      </c>
-      <c r="C50">
-        <v>19</v>
+        <v>39</v>
+      </c>
+      <c r="C50" t="s">
+        <v>180</v>
       </c>
       <c r="D50">
         <v>1</v>
       </c>
       <c r="E50" t="s">
-        <v>22</v>
+        <v>21</v>
       </c>
       <c r="F50" t="s">
+        <v>138</v>
+      </c>
+      <c r="G50" t="s">
         <v>139</v>
       </c>
-      <c r="G50" t="s">
-        <v>140</v>
-      </c>
       <c r="H50" t="s">
-        <v>24</v>
+        <v>23</v>
       </c>
       <c r="I50">
         <v>4000</v>
       </c>
       <c r="J50" t="s">
-        <v>229</v>
-      </c>
-      <c r="K50" t="s">
-        <v>15</v>
-      </c>
-    </row>
-    <row r="51" spans="1:11" x14ac:dyDescent="0.25">
+        <v>235</v>
+      </c>
+    </row>
+    <row r="51" spans="1:10" x14ac:dyDescent="0.25">
       <c r="A51" t="s">
-        <v>21</v>
+        <v>20</v>
       </c>
       <c r="B51" t="s">
-        <v>53</v>
-      </c>
-      <c r="C51">
-        <v>5</v>
+        <v>52</v>
+      </c>
+      <c r="C51" t="s">
+        <v>184</v>
       </c>
       <c r="D51">
         <v>1</v>
       </c>
+      <c r="E51" t="s">
+        <v>211</v>
+      </c>
       <c r="F51" t="s">
+        <v>140</v>
+      </c>
+      <c r="G51" t="s">
         <v>141</v>
       </c>
-      <c r="G51" t="s">
-        <v>142</v>
-      </c>
       <c r="H51" t="s">
-        <v>17</v>
+        <v>16</v>
       </c>
       <c r="I51">
         <v>700</v>
       </c>
       <c r="J51" t="s">
-        <v>230</v>
-      </c>
-      <c r="K51" t="s">
-        <v>15</v>
-      </c>
-    </row>
-    <row r="52" spans="1:11" x14ac:dyDescent="0.25">
+        <v>236</v>
+      </c>
+    </row>
+    <row r="52" spans="1:10" x14ac:dyDescent="0.25">
       <c r="A52" t="s">
-        <v>21</v>
+        <v>20</v>
       </c>
       <c r="B52" t="s">
         <v>12</v>
       </c>
-      <c r="C52">
-        <v>19</v>
+      <c r="C52" t="s">
+        <v>180</v>
       </c>
       <c r="D52">
         <v>1</v>
       </c>
+      <c r="E52" t="s">
+        <v>189</v>
+      </c>
       <c r="F52" t="s">
+        <v>142</v>
+      </c>
+      <c r="G52" t="s">
         <v>143</v>
       </c>
-      <c r="G52" t="s">
+      <c r="H52" t="s">
         <v>144</v>
-      </c>
-      <c r="H52" t="s">
-        <v>145</v>
       </c>
       <c r="I52">
         <v>600</v>
       </c>
       <c r="J52" t="s">
-        <v>231</v>
-      </c>
-      <c r="K52" t="s">
-        <v>15</v>
-      </c>
-    </row>
-    <row r="53" spans="1:11" x14ac:dyDescent="0.25">
+        <v>237</v>
+      </c>
+    </row>
+    <row r="53" spans="1:10" x14ac:dyDescent="0.25">
       <c r="A53" t="s">
-        <v>21</v>
+        <v>20</v>
       </c>
       <c r="B53" t="s">
-        <v>34</v>
-      </c>
-      <c r="C53">
-        <v>5</v>
+        <v>33</v>
+      </c>
+      <c r="C53" t="s">
+        <v>184</v>
       </c>
       <c r="D53">
         <v>1</v>
       </c>
+      <c r="E53" t="s">
+        <v>189</v>
+      </c>
       <c r="F53" t="s">
-        <v>146</v>
+        <v>145</v>
       </c>
       <c r="G53" t="s">
-        <v>110</v>
+        <v>109</v>
       </c>
       <c r="H53" t="s">
-        <v>24</v>
+        <v>23</v>
       </c>
       <c r="I53">
         <v>700</v>
       </c>
       <c r="J53" t="s">
-        <v>232</v>
-      </c>
-      <c r="K53" t="s">
-        <v>15</v>
-      </c>
-    </row>
-    <row r="54" spans="1:11" x14ac:dyDescent="0.25">
+        <v>238</v>
+      </c>
+    </row>
+    <row r="54" spans="1:10" x14ac:dyDescent="0.25">
       <c r="A54" t="s">
-        <v>21</v>
+        <v>20</v>
       </c>
       <c r="B54" t="s">
-        <v>34</v>
-      </c>
-      <c r="C54">
-        <v>5</v>
+        <v>33</v>
+      </c>
+      <c r="C54" t="s">
+        <v>184</v>
       </c>
       <c r="D54">
         <v>2</v>
       </c>
+      <c r="E54" t="s">
+        <v>189</v>
+      </c>
       <c r="F54" t="s">
-        <v>147</v>
+        <v>146</v>
       </c>
       <c r="G54" t="s">
-        <v>110</v>
+        <v>109</v>
       </c>
       <c r="H54" t="s">
-        <v>24</v>
+        <v>23</v>
       </c>
       <c r="I54">
         <v>700</v>
       </c>
       <c r="J54" t="s">
-        <v>233</v>
-      </c>
-      <c r="K54" t="s">
-        <v>15</v>
-      </c>
-    </row>
-    <row r="55" spans="1:11" x14ac:dyDescent="0.25">
+        <v>239</v>
+      </c>
+    </row>
+    <row r="55" spans="1:10" x14ac:dyDescent="0.25">
       <c r="A55" t="s">
-        <v>21</v>
+        <v>20</v>
       </c>
       <c r="B55" t="s">
+        <v>41</v>
+      </c>
+      <c r="C55" t="s">
+        <v>180</v>
+      </c>
+      <c r="D55">
+        <v>1</v>
+      </c>
+      <c r="E55" t="s">
         <v>42</v>
       </c>
-      <c r="C55">
-        <v>19</v>
-      </c>
-      <c r="D55">
-        <v>1</v>
-      </c>
-      <c r="E55" t="s">
+      <c r="F55" t="s">
         <v>43</v>
       </c>
-      <c r="F55" t="s">
+      <c r="G55" t="s">
         <v>44</v>
       </c>
-      <c r="G55" t="s">
-        <v>45</v>
-      </c>
       <c r="H55" t="s">
-        <v>35</v>
+        <v>34</v>
       </c>
       <c r="I55">
         <v>350</v>
       </c>
       <c r="J55" t="s">
-        <v>234</v>
-      </c>
-      <c r="K55" t="s">
-        <v>15</v>
-      </c>
-    </row>
-    <row r="56" spans="1:11" x14ac:dyDescent="0.25">
+        <v>240</v>
+      </c>
+    </row>
+    <row r="56" spans="1:10" x14ac:dyDescent="0.25">
       <c r="A56" t="s">
-        <v>21</v>
+        <v>20</v>
       </c>
       <c r="B56" t="s">
         <v>12</v>
       </c>
-      <c r="C56">
-        <v>19</v>
+      <c r="C56" t="s">
+        <v>180</v>
       </c>
       <c r="D56">
         <v>1</v>
       </c>
+      <c r="E56" t="s">
+        <v>189</v>
+      </c>
       <c r="F56" t="s">
-        <v>148</v>
+        <v>147</v>
       </c>
       <c r="G56" t="s">
+        <v>143</v>
+      </c>
+      <c r="H56" t="s">
         <v>144</v>
-      </c>
-      <c r="H56" t="s">
-        <v>145</v>
       </c>
       <c r="I56">
         <v>600</v>
       </c>
       <c r="J56" t="s">
-        <v>235</v>
-      </c>
-      <c r="K56" t="s">
+        <v>241</v>
+      </c>
+    </row>
+    <row r="57" spans="1:10" x14ac:dyDescent="0.25">
+      <c r="A57" t="s">
+        <v>20</v>
+      </c>
+      <c r="B57" t="s">
         <v>15</v>
       </c>
-    </row>
-    <row r="57" spans="1:11" x14ac:dyDescent="0.25">
-      <c r="A57" t="s">
-        <v>21</v>
-      </c>
-      <c r="B57" t="s">
-        <v>16</v>
-      </c>
-      <c r="C57">
-        <v>5</v>
+      <c r="C57" t="s">
+        <v>184</v>
       </c>
       <c r="D57">
         <v>1</v>
       </c>
       <c r="E57" t="s">
+        <v>66</v>
+      </c>
+      <c r="F57" t="s">
         <v>67</v>
       </c>
-      <c r="F57" t="s">
-        <v>68</v>
-      </c>
       <c r="G57" t="s">
-        <v>37</v>
+        <v>36</v>
       </c>
       <c r="H57" t="s">
         <v>14</v>
@@ -3074,33 +3179,30 @@
         <v>220</v>
       </c>
       <c r="J57" t="s">
-        <v>236</v>
-      </c>
-      <c r="K57" t="s">
+        <v>242</v>
+      </c>
+    </row>
+    <row r="58" spans="1:10" x14ac:dyDescent="0.25">
+      <c r="A58" t="s">
+        <v>20</v>
+      </c>
+      <c r="B58" t="s">
         <v>15</v>
       </c>
-    </row>
-    <row r="58" spans="1:11" x14ac:dyDescent="0.25">
-      <c r="A58" t="s">
-        <v>21</v>
-      </c>
-      <c r="B58" t="s">
-        <v>16</v>
-      </c>
-      <c r="C58">
-        <v>5</v>
+      <c r="C58" t="s">
+        <v>184</v>
       </c>
       <c r="D58">
         <v>1</v>
       </c>
       <c r="E58" t="s">
+        <v>64</v>
+      </c>
+      <c r="F58" t="s">
         <v>65</v>
       </c>
-      <c r="F58" t="s">
-        <v>66</v>
-      </c>
       <c r="G58" t="s">
-        <v>37</v>
+        <v>36</v>
       </c>
       <c r="H58" t="s">
         <v>14</v>
@@ -3109,33 +3211,30 @@
         <v>220</v>
       </c>
       <c r="J58" t="s">
-        <v>237</v>
-      </c>
-      <c r="K58" t="s">
+        <v>243</v>
+      </c>
+    </row>
+    <row r="59" spans="1:10" x14ac:dyDescent="0.25">
+      <c r="A59" t="s">
+        <v>20</v>
+      </c>
+      <c r="B59" t="s">
         <v>15</v>
       </c>
-    </row>
-    <row r="59" spans="1:11" x14ac:dyDescent="0.25">
-      <c r="A59" t="s">
-        <v>21</v>
-      </c>
-      <c r="B59" t="s">
-        <v>16</v>
-      </c>
-      <c r="C59">
-        <v>5</v>
+      <c r="C59" t="s">
+        <v>184</v>
       </c>
       <c r="D59">
         <v>1</v>
       </c>
       <c r="E59" t="s">
+        <v>62</v>
+      </c>
+      <c r="F59" t="s">
         <v>63</v>
       </c>
-      <c r="F59" t="s">
-        <v>64</v>
-      </c>
       <c r="G59" t="s">
-        <v>37</v>
+        <v>36</v>
       </c>
       <c r="H59" t="s">
         <v>14</v>
@@ -3144,30 +3243,30 @@
         <v>220</v>
       </c>
       <c r="J59" t="s">
-        <v>238</v>
-      </c>
-      <c r="K59" t="s">
+        <v>244</v>
+      </c>
+    </row>
+    <row r="60" spans="1:10" x14ac:dyDescent="0.25">
+      <c r="A60" t="s">
+        <v>20</v>
+      </c>
+      <c r="B60" t="s">
         <v>15</v>
       </c>
-    </row>
-    <row r="60" spans="1:11" x14ac:dyDescent="0.25">
-      <c r="A60" t="s">
-        <v>21</v>
-      </c>
-      <c r="B60" t="s">
-        <v>16</v>
-      </c>
-      <c r="C60">
-        <v>5</v>
+      <c r="C60" t="s">
+        <v>184</v>
       </c>
       <c r="D60">
         <v>1</v>
       </c>
+      <c r="E60" t="s">
+        <v>189</v>
+      </c>
       <c r="F60" t="s">
-        <v>149</v>
+        <v>148</v>
       </c>
       <c r="G60" t="s">
-        <v>37</v>
+        <v>36</v>
       </c>
       <c r="H60" t="s">
         <v>14</v>
@@ -3176,464 +3275,446 @@
         <v>2500</v>
       </c>
       <c r="J60" t="s">
-        <v>239</v>
-      </c>
-      <c r="K60" t="s">
-        <v>15</v>
-      </c>
-    </row>
-    <row r="61" spans="1:11" x14ac:dyDescent="0.25">
+        <v>245</v>
+      </c>
+    </row>
+    <row r="61" spans="1:10" x14ac:dyDescent="0.25">
       <c r="A61" t="s">
-        <v>21</v>
+        <v>20</v>
       </c>
       <c r="B61" t="s">
-        <v>27</v>
-      </c>
-      <c r="C61">
-        <v>19</v>
+        <v>26</v>
+      </c>
+      <c r="C61" t="s">
+        <v>180</v>
       </c>
       <c r="D61">
         <v>2</v>
       </c>
       <c r="E61" t="s">
-        <v>31</v>
+        <v>30</v>
       </c>
       <c r="F61" t="s">
-        <v>48</v>
+        <v>47</v>
       </c>
       <c r="G61" t="s">
+        <v>27</v>
+      </c>
+      <c r="H61" t="s">
         <v>28</v>
-      </c>
-      <c r="H61" t="s">
-        <v>29</v>
       </c>
       <c r="I61">
         <v>600</v>
       </c>
       <c r="J61" t="s">
-        <v>240</v>
-      </c>
-      <c r="K61" t="s">
-        <v>15</v>
-      </c>
-    </row>
-    <row r="62" spans="1:11" x14ac:dyDescent="0.25">
+        <v>246</v>
+      </c>
+    </row>
+    <row r="62" spans="1:10" x14ac:dyDescent="0.25">
       <c r="A62" t="s">
-        <v>21</v>
+        <v>20</v>
       </c>
       <c r="B62" t="s">
-        <v>27</v>
-      </c>
-      <c r="C62">
-        <v>19</v>
+        <v>26</v>
+      </c>
+      <c r="C62" t="s">
+        <v>180</v>
       </c>
       <c r="D62">
         <v>6</v>
       </c>
       <c r="E62" t="s">
-        <v>81</v>
+        <v>80</v>
       </c>
       <c r="F62" t="s">
-        <v>150</v>
+        <v>149</v>
       </c>
       <c r="G62" t="s">
-        <v>41</v>
+        <v>40</v>
       </c>
       <c r="H62" t="s">
-        <v>29</v>
+        <v>28</v>
       </c>
       <c r="I62">
         <v>1700</v>
       </c>
       <c r="J62" t="s">
-        <v>241</v>
-      </c>
-      <c r="K62" t="s">
-        <v>15</v>
-      </c>
-    </row>
-    <row r="63" spans="1:11" x14ac:dyDescent="0.25">
+        <v>247</v>
+      </c>
+    </row>
+    <row r="63" spans="1:10" x14ac:dyDescent="0.25">
       <c r="A63" t="s">
-        <v>21</v>
+        <v>20</v>
       </c>
       <c r="B63" t="s">
-        <v>151</v>
-      </c>
-      <c r="C63">
-        <v>12</v>
+        <v>150</v>
+      </c>
+      <c r="C63" t="s">
+        <v>231</v>
       </c>
       <c r="D63">
         <v>3</v>
       </c>
+      <c r="E63" t="s">
+        <v>189</v>
+      </c>
       <c r="F63" t="s">
+        <v>151</v>
+      </c>
+      <c r="G63" t="s">
         <v>152</v>
       </c>
-      <c r="G63" t="s">
-        <v>153</v>
-      </c>
       <c r="H63" t="s">
-        <v>29</v>
+        <v>28</v>
       </c>
       <c r="I63">
         <v>350</v>
       </c>
       <c r="J63" t="s">
-        <v>242</v>
-      </c>
-      <c r="K63" t="s">
-        <v>15</v>
-      </c>
-    </row>
-    <row r="64" spans="1:11" x14ac:dyDescent="0.25">
+        <v>248</v>
+      </c>
+    </row>
+    <row r="64" spans="1:10" x14ac:dyDescent="0.25">
       <c r="A64" t="s">
-        <v>21</v>
+        <v>20</v>
       </c>
       <c r="B64" t="s">
+        <v>153</v>
+      </c>
+      <c r="C64" t="s">
+        <v>180</v>
+      </c>
+      <c r="D64">
+        <v>1</v>
+      </c>
+      <c r="E64" t="s">
+        <v>211</v>
+      </c>
+      <c r="F64" t="s">
         <v>154</v>
       </c>
-      <c r="C64">
-        <v>19</v>
-      </c>
-      <c r="D64">
-        <v>1</v>
-      </c>
-      <c r="F64" t="s">
+      <c r="G64" t="s">
+        <v>95</v>
+      </c>
+      <c r="H64" t="s">
         <v>155</v>
-      </c>
-      <c r="G64" t="s">
-        <v>96</v>
-      </c>
-      <c r="H64" t="s">
-        <v>156</v>
       </c>
       <c r="I64">
         <v>960</v>
       </c>
       <c r="J64" t="s">
-        <v>243</v>
-      </c>
-      <c r="K64" t="s">
-        <v>15</v>
-      </c>
-    </row>
-    <row r="65" spans="1:11" x14ac:dyDescent="0.25">
+        <v>249</v>
+      </c>
+    </row>
+    <row r="65" spans="1:10" x14ac:dyDescent="0.25">
       <c r="A65" t="s">
-        <v>21</v>
+        <v>20</v>
       </c>
       <c r="B65" t="s">
-        <v>116</v>
-      </c>
-      <c r="C65">
-        <v>19</v>
+        <v>115</v>
+      </c>
+      <c r="C65" t="s">
+        <v>180</v>
       </c>
       <c r="D65">
         <v>1</v>
       </c>
+      <c r="E65" t="s">
+        <v>195</v>
+      </c>
       <c r="F65" t="s">
+        <v>156</v>
+      </c>
+      <c r="G65" t="s">
         <v>157</v>
       </c>
-      <c r="G65" t="s">
-        <v>158</v>
-      </c>
       <c r="H65" t="s">
-        <v>24</v>
+        <v>23</v>
       </c>
       <c r="I65">
         <v>1600</v>
       </c>
       <c r="J65" t="s">
-        <v>244</v>
-      </c>
-      <c r="K65" t="s">
-        <v>15</v>
-      </c>
-    </row>
-    <row r="66" spans="1:11" x14ac:dyDescent="0.25">
+        <v>250</v>
+      </c>
+    </row>
+    <row r="66" spans="1:10" x14ac:dyDescent="0.25">
       <c r="A66" t="s">
-        <v>21</v>
+        <v>20</v>
       </c>
       <c r="B66" t="s">
-        <v>120</v>
-      </c>
-      <c r="C66">
-        <v>3</v>
+        <v>119</v>
+      </c>
+      <c r="C66" t="s">
+        <v>214</v>
       </c>
       <c r="D66">
         <v>1</v>
       </c>
+      <c r="E66" t="s">
+        <v>189</v>
+      </c>
       <c r="F66" t="s">
-        <v>159</v>
+        <v>158</v>
       </c>
       <c r="G66" t="s">
+        <v>121</v>
+      </c>
+      <c r="H66" t="s">
         <v>122</v>
-      </c>
-      <c r="H66" t="s">
-        <v>123</v>
       </c>
       <c r="I66">
         <v>750</v>
       </c>
       <c r="J66" t="s">
-        <v>245</v>
-      </c>
-      <c r="K66" t="s">
-        <v>15</v>
-      </c>
-    </row>
-    <row r="67" spans="1:11" x14ac:dyDescent="0.25">
+        <v>251</v>
+      </c>
+    </row>
+    <row r="67" spans="1:10" x14ac:dyDescent="0.25">
       <c r="A67" t="s">
-        <v>21</v>
+        <v>20</v>
       </c>
       <c r="B67" t="s">
-        <v>98</v>
-      </c>
-      <c r="C67">
-        <v>5</v>
+        <v>97</v>
+      </c>
+      <c r="C67" t="s">
+        <v>184</v>
       </c>
       <c r="D67">
         <v>1</v>
       </c>
+      <c r="E67" t="s">
+        <v>189</v>
+      </c>
       <c r="F67" t="s">
-        <v>160</v>
+        <v>159</v>
       </c>
       <c r="G67" t="s">
+        <v>99</v>
+      </c>
+      <c r="H67" t="s">
         <v>100</v>
-      </c>
-      <c r="H67" t="s">
-        <v>101</v>
       </c>
       <c r="I67">
         <v>560</v>
       </c>
       <c r="J67" t="s">
-        <v>246</v>
-      </c>
-      <c r="K67" t="s">
-        <v>15</v>
-      </c>
-    </row>
-    <row r="68" spans="1:11" x14ac:dyDescent="0.25">
+        <v>252</v>
+      </c>
+    </row>
+    <row r="68" spans="1:10" x14ac:dyDescent="0.25">
       <c r="A68" t="s">
-        <v>21</v>
+        <v>20</v>
       </c>
       <c r="B68" t="s">
-        <v>82</v>
-      </c>
-      <c r="C68">
-        <v>5</v>
+        <v>81</v>
+      </c>
+      <c r="C68" t="s">
+        <v>184</v>
       </c>
       <c r="D68">
         <v>75</v>
       </c>
+      <c r="E68" t="s">
+        <v>195</v>
+      </c>
       <c r="F68" t="s">
-        <v>161</v>
+        <v>160</v>
       </c>
       <c r="G68" t="s">
-        <v>85</v>
+        <v>84</v>
       </c>
       <c r="H68" t="s">
-        <v>17</v>
+        <v>16</v>
       </c>
       <c r="I68">
         <v>650</v>
       </c>
       <c r="J68" t="s">
-        <v>247</v>
-      </c>
-      <c r="K68" t="s">
-        <v>15</v>
-      </c>
-    </row>
-    <row r="69" spans="1:11" x14ac:dyDescent="0.25">
+        <v>253</v>
+      </c>
+    </row>
+    <row r="69" spans="1:10" x14ac:dyDescent="0.25">
       <c r="A69" t="s">
-        <v>21</v>
+        <v>20</v>
       </c>
       <c r="B69" t="s">
-        <v>82</v>
-      </c>
-      <c r="C69">
-        <v>5</v>
+        <v>81</v>
+      </c>
+      <c r="C69" t="s">
+        <v>184</v>
       </c>
       <c r="D69">
         <v>20</v>
       </c>
+      <c r="E69" t="s">
+        <v>195</v>
+      </c>
       <c r="F69" t="s">
-        <v>162</v>
+        <v>161</v>
       </c>
       <c r="G69" t="s">
-        <v>85</v>
+        <v>84</v>
       </c>
       <c r="H69" t="s">
-        <v>17</v>
+        <v>16</v>
       </c>
       <c r="I69">
         <v>4000</v>
       </c>
       <c r="J69" t="s">
-        <v>248</v>
-      </c>
-      <c r="K69" t="s">
-        <v>15</v>
-      </c>
-    </row>
-    <row r="70" spans="1:11" x14ac:dyDescent="0.25">
+        <v>254</v>
+      </c>
+    </row>
+    <row r="70" spans="1:10" x14ac:dyDescent="0.25">
       <c r="A70" t="s">
-        <v>21</v>
+        <v>20</v>
       </c>
       <c r="B70" t="s">
-        <v>27</v>
-      </c>
-      <c r="C70">
-        <v>19</v>
+        <v>26</v>
+      </c>
+      <c r="C70" t="s">
+        <v>180</v>
       </c>
       <c r="D70">
         <v>2</v>
       </c>
       <c r="E70" t="s">
-        <v>30</v>
+        <v>29</v>
       </c>
       <c r="F70" t="s">
-        <v>166</v>
+        <v>165</v>
       </c>
       <c r="G70" t="s">
-        <v>41</v>
+        <v>40</v>
       </c>
       <c r="H70" t="s">
-        <v>29</v>
+        <v>28</v>
       </c>
       <c r="I70">
         <v>600</v>
       </c>
       <c r="J70" t="s">
-        <v>249</v>
-      </c>
-      <c r="K70" t="s">
-        <v>15</v>
-      </c>
-    </row>
-    <row r="71" spans="1:11" x14ac:dyDescent="0.25">
+        <v>255</v>
+      </c>
+    </row>
+    <row r="71" spans="1:10" x14ac:dyDescent="0.25">
       <c r="A71" t="s">
+        <v>166</v>
+      </c>
+      <c r="B71" t="s">
         <v>167</v>
       </c>
-      <c r="B71" t="s">
+      <c r="C71" t="s">
+        <v>214</v>
+      </c>
+      <c r="D71">
+        <v>1</v>
+      </c>
+      <c r="E71" t="s">
         <v>168</v>
       </c>
-      <c r="C71">
-        <v>3</v>
-      </c>
-      <c r="D71">
-        <v>1</v>
-      </c>
-      <c r="E71" t="s">
+      <c r="F71" t="s">
         <v>169</v>
       </c>
-      <c r="F71" t="s">
-        <v>170</v>
-      </c>
       <c r="G71" t="s">
+        <v>121</v>
+      </c>
+      <c r="H71" t="s">
         <v>122</v>
-      </c>
-      <c r="H71" t="s">
-        <v>123</v>
       </c>
       <c r="I71">
         <v>500</v>
       </c>
       <c r="J71" t="s">
-        <v>250</v>
-      </c>
-      <c r="K71" t="s">
-        <v>15</v>
-      </c>
-    </row>
-    <row r="72" spans="1:11" x14ac:dyDescent="0.25">
+        <v>256</v>
+      </c>
+    </row>
+    <row r="72" spans="1:10" x14ac:dyDescent="0.25">
       <c r="A72" t="s">
-        <v>167</v>
+        <v>166</v>
       </c>
       <c r="B72" t="s">
+        <v>170</v>
+      </c>
+      <c r="C72" t="s">
+        <v>257</v>
+      </c>
+      <c r="D72">
+        <v>1</v>
+      </c>
+      <c r="E72" t="s">
+        <v>38</v>
+      </c>
+      <c r="F72" t="s">
         <v>171</v>
       </c>
-      <c r="C72">
-        <v>6</v>
-      </c>
-      <c r="D72">
-        <v>1</v>
-      </c>
-      <c r="E72" t="s">
-        <v>39</v>
-      </c>
-      <c r="F72" t="s">
+      <c r="G72" t="s">
         <v>172</v>
       </c>
-      <c r="G72" t="s">
+      <c r="H72" t="s">
         <v>173</v>
-      </c>
-      <c r="H72" t="s">
-        <v>174</v>
       </c>
       <c r="I72">
         <v>400</v>
       </c>
       <c r="J72" t="s">
-        <v>251</v>
-      </c>
-      <c r="K72" t="s">
-        <v>15</v>
-      </c>
-    </row>
-    <row r="73" spans="1:11" x14ac:dyDescent="0.25">
+        <v>258</v>
+      </c>
+    </row>
+    <row r="73" spans="1:10" x14ac:dyDescent="0.25">
       <c r="A73" t="s">
-        <v>167</v>
+        <v>166</v>
       </c>
       <c r="B73" t="s">
-        <v>163</v>
-      </c>
-      <c r="C73">
-        <v>5</v>
+        <v>162</v>
+      </c>
+      <c r="C73" t="s">
+        <v>184</v>
       </c>
       <c r="D73">
         <v>2</v>
       </c>
+      <c r="E73" t="s">
+        <v>195</v>
+      </c>
       <c r="F73" t="s">
-        <v>175</v>
+        <v>174</v>
       </c>
       <c r="G73" t="s">
+        <v>163</v>
+      </c>
+      <c r="H73" t="s">
         <v>164</v>
-      </c>
-      <c r="H73" t="s">
-        <v>165</v>
       </c>
       <c r="I73">
         <v>350</v>
       </c>
       <c r="J73" t="s">
-        <v>252</v>
-      </c>
-      <c r="K73" t="s">
+        <v>259</v>
+      </c>
+    </row>
+    <row r="74" spans="1:10" x14ac:dyDescent="0.25">
+      <c r="A74" t="s">
+        <v>166</v>
+      </c>
+      <c r="B74" t="s">
         <v>15</v>
       </c>
-    </row>
-    <row r="74" spans="1:11" x14ac:dyDescent="0.25">
-      <c r="A74" t="s">
-        <v>167</v>
-      </c>
-      <c r="B74" t="s">
-        <v>16</v>
-      </c>
-      <c r="C74">
-        <v>5</v>
+      <c r="C74" t="s">
+        <v>184</v>
       </c>
       <c r="D74">
         <v>1</v>
       </c>
       <c r="E74" t="s">
+        <v>175</v>
+      </c>
+      <c r="F74" t="s">
         <v>176</v>
       </c>
-      <c r="F74" t="s">
-        <v>177</v>
-      </c>
       <c r="G74" t="s">
-        <v>37</v>
+        <v>36</v>
       </c>
       <c r="H74" t="s">
         <v>14</v>
@@ -3642,45 +3723,455 @@
         <v>500</v>
       </c>
       <c r="J74" t="s">
-        <v>253</v>
-      </c>
-      <c r="K74" t="s">
-        <v>15</v>
-      </c>
-    </row>
-    <row r="75" spans="1:11" x14ac:dyDescent="0.25">
+        <v>260</v>
+      </c>
+    </row>
+    <row r="75" spans="1:10" x14ac:dyDescent="0.25">
       <c r="A75" t="s">
-        <v>167</v>
+        <v>166</v>
       </c>
       <c r="B75" t="s">
+        <v>177</v>
+      </c>
+      <c r="C75" t="s">
+        <v>184</v>
+      </c>
+      <c r="D75">
+        <v>1</v>
+      </c>
+      <c r="E75" t="s">
+        <v>21</v>
+      </c>
+      <c r="F75" t="s">
         <v>178</v>
       </c>
-      <c r="C75">
-        <v>5</v>
-      </c>
-      <c r="D75">
-        <v>1</v>
-      </c>
-      <c r="E75" t="s">
-        <v>22</v>
-      </c>
-      <c r="F75" t="s">
+      <c r="G75" t="s">
         <v>179</v>
       </c>
-      <c r="G75" t="s">
-        <v>180</v>
-      </c>
       <c r="H75" t="s">
-        <v>123</v>
+        <v>122</v>
       </c>
       <c r="I75">
         <v>250</v>
       </c>
       <c r="J75" t="s">
-        <v>254</v>
-      </c>
-      <c r="K75" t="s">
-        <v>15</v>
+        <v>261</v>
+      </c>
+    </row>
+    <row r="76" spans="1:10" x14ac:dyDescent="0.25">
+      <c r="A76" t="s">
+        <v>166</v>
+      </c>
+      <c r="B76" t="s">
+        <v>262</v>
+      </c>
+      <c r="C76" t="s">
+        <v>184</v>
+      </c>
+      <c r="D76">
+        <v>1</v>
+      </c>
+      <c r="E76" t="s">
+        <v>263</v>
+      </c>
+      <c r="F76" t="s">
+        <v>264</v>
+      </c>
+      <c r="G76" t="s">
+        <v>70</v>
+      </c>
+      <c r="H76" t="s">
+        <v>14</v>
+      </c>
+      <c r="I76">
+        <v>500</v>
+      </c>
+      <c r="J76" t="s">
+        <v>265</v>
+      </c>
+    </row>
+    <row r="77" spans="1:10" x14ac:dyDescent="0.25">
+      <c r="A77" t="s">
+        <v>266</v>
+      </c>
+      <c r="B77" t="s">
+        <v>267</v>
+      </c>
+      <c r="C77" t="s">
+        <v>268</v>
+      </c>
+      <c r="D77">
+        <v>1</v>
+      </c>
+      <c r="E77" t="s">
+        <v>269</v>
+      </c>
+      <c r="F77" t="s">
+        <v>270</v>
+      </c>
+      <c r="G77" t="s">
+        <v>271</v>
+      </c>
+      <c r="H77" t="s">
+        <v>272</v>
+      </c>
+      <c r="I77">
+        <v>800</v>
+      </c>
+      <c r="J77" t="s">
+        <v>273</v>
+      </c>
+    </row>
+    <row r="78" spans="1:10" x14ac:dyDescent="0.25">
+      <c r="A78" t="s">
+        <v>266</v>
+      </c>
+      <c r="B78" t="s">
+        <v>267</v>
+      </c>
+      <c r="C78" t="s">
+        <v>268</v>
+      </c>
+      <c r="D78">
+        <v>1</v>
+      </c>
+      <c r="E78" t="s">
+        <v>274</v>
+      </c>
+      <c r="F78" t="s">
+        <v>275</v>
+      </c>
+      <c r="G78" t="s">
+        <v>271</v>
+      </c>
+      <c r="H78" t="s">
+        <v>272</v>
+      </c>
+      <c r="I78">
+        <v>600</v>
+      </c>
+      <c r="J78" t="s">
+        <v>276</v>
+      </c>
+    </row>
+    <row r="79" spans="1:10" x14ac:dyDescent="0.25">
+      <c r="A79" t="s">
+        <v>266</v>
+      </c>
+      <c r="B79" t="s">
+        <v>267</v>
+      </c>
+      <c r="C79" t="s">
+        <v>268</v>
+      </c>
+      <c r="D79">
+        <v>1</v>
+      </c>
+      <c r="E79" t="s">
+        <v>277</v>
+      </c>
+      <c r="F79" t="s">
+        <v>275</v>
+      </c>
+      <c r="G79" t="s">
+        <v>271</v>
+      </c>
+      <c r="H79" t="s">
+        <v>272</v>
+      </c>
+      <c r="I79">
+        <v>600</v>
+      </c>
+      <c r="J79" t="s">
+        <v>278</v>
+      </c>
+    </row>
+    <row r="80" spans="1:10" x14ac:dyDescent="0.25">
+      <c r="A80" t="s">
+        <v>279</v>
+      </c>
+      <c r="B80" t="s">
+        <v>280</v>
+      </c>
+      <c r="C80" t="s">
+        <v>281</v>
+      </c>
+      <c r="D80">
+        <v>26</v>
+      </c>
+      <c r="E80" t="s">
+        <v>282</v>
+      </c>
+      <c r="F80" t="s">
+        <v>283</v>
+      </c>
+      <c r="G80" t="s">
+        <v>284</v>
+      </c>
+      <c r="H80" t="s">
+        <v>28</v>
+      </c>
+      <c r="I80">
+        <v>520</v>
+      </c>
+      <c r="J80" t="s">
+        <v>285</v>
+      </c>
+    </row>
+    <row r="81" spans="1:10" x14ac:dyDescent="0.25">
+      <c r="A81" t="s">
+        <v>286</v>
+      </c>
+      <c r="B81" t="s">
+        <v>287</v>
+      </c>
+      <c r="C81" t="s">
+        <v>180</v>
+      </c>
+      <c r="D81">
+        <v>50</v>
+      </c>
+      <c r="E81" t="s">
+        <v>288</v>
+      </c>
+      <c r="F81" t="s">
+        <v>289</v>
+      </c>
+      <c r="G81" t="s">
+        <v>40</v>
+      </c>
+      <c r="H81" t="s">
+        <v>28</v>
+      </c>
+      <c r="I81">
+        <v>6000</v>
+      </c>
+      <c r="J81" t="s">
+        <v>290</v>
+      </c>
+    </row>
+    <row r="82" spans="1:10" x14ac:dyDescent="0.25">
+      <c r="A82" t="s">
+        <v>286</v>
+      </c>
+      <c r="B82" t="s">
+        <v>162</v>
+      </c>
+      <c r="C82" t="s">
+        <v>184</v>
+      </c>
+      <c r="D82">
+        <v>1</v>
+      </c>
+      <c r="E82" t="s">
+        <v>189</v>
+      </c>
+      <c r="F82" t="s">
+        <v>291</v>
+      </c>
+      <c r="G82" t="s">
+        <v>292</v>
+      </c>
+      <c r="H82" t="s">
+        <v>14</v>
+      </c>
+      <c r="I82">
+        <v>1000</v>
+      </c>
+      <c r="J82" t="s">
+        <v>293</v>
+      </c>
+    </row>
+    <row r="83" spans="1:10" x14ac:dyDescent="0.25">
+      <c r="A83" t="s">
+        <v>166</v>
+      </c>
+      <c r="B83" t="s">
+        <v>294</v>
+      </c>
+      <c r="C83" t="s">
+        <v>180</v>
+      </c>
+      <c r="D83">
+        <v>20</v>
+      </c>
+      <c r="E83" t="s">
+        <v>195</v>
+      </c>
+      <c r="F83" t="s">
+        <v>295</v>
+      </c>
+      <c r="G83" t="s">
+        <v>117</v>
+      </c>
+      <c r="H83" t="s">
+        <v>28</v>
+      </c>
+      <c r="I83">
+        <v>360</v>
+      </c>
+      <c r="J83" t="s">
+        <v>296</v>
+      </c>
+    </row>
+    <row r="84" spans="1:10" x14ac:dyDescent="0.25">
+      <c r="A84" t="s">
+        <v>286</v>
+      </c>
+      <c r="B84" t="s">
+        <v>297</v>
+      </c>
+      <c r="C84" t="s">
+        <v>298</v>
+      </c>
+      <c r="D84">
+        <v>2</v>
+      </c>
+      <c r="E84" t="s">
+        <v>189</v>
+      </c>
+      <c r="F84" t="s">
+        <v>299</v>
+      </c>
+      <c r="G84" t="s">
+        <v>300</v>
+      </c>
+      <c r="H84" t="s">
+        <v>14</v>
+      </c>
+      <c r="I84">
+        <v>800</v>
+      </c>
+      <c r="J84" t="s">
+        <v>301</v>
+      </c>
+    </row>
+    <row r="85" spans="1:10" x14ac:dyDescent="0.25">
+      <c r="A85" t="s">
+        <v>166</v>
+      </c>
+      <c r="B85" t="s">
+        <v>302</v>
+      </c>
+      <c r="C85" t="s">
+        <v>214</v>
+      </c>
+      <c r="D85">
+        <v>2</v>
+      </c>
+      <c r="E85" t="s">
+        <v>211</v>
+      </c>
+      <c r="F85" t="s">
+        <v>303</v>
+      </c>
+      <c r="G85" t="s">
+        <v>304</v>
+      </c>
+      <c r="H85" t="s">
+        <v>14</v>
+      </c>
+      <c r="I85">
+        <v>540</v>
+      </c>
+      <c r="J85" t="s">
+        <v>305</v>
+      </c>
+    </row>
+    <row r="86" spans="1:10" x14ac:dyDescent="0.25">
+      <c r="A86" t="s">
+        <v>11</v>
+      </c>
+      <c r="B86" t="s">
+        <v>37</v>
+      </c>
+      <c r="C86" t="s">
+        <v>180</v>
+      </c>
+      <c r="D86">
+        <v>1</v>
+      </c>
+      <c r="E86" t="s">
+        <v>306</v>
+      </c>
+      <c r="F86" t="s">
+        <v>307</v>
+      </c>
+      <c r="G86" t="s">
+        <v>27</v>
+      </c>
+      <c r="H86" t="s">
+        <v>28</v>
+      </c>
+      <c r="I86">
+        <v>1920</v>
+      </c>
+      <c r="J86" t="s">
+        <v>308</v>
+      </c>
+    </row>
+    <row r="87" spans="1:10" x14ac:dyDescent="0.25">
+      <c r="A87" t="s">
+        <v>309</v>
+      </c>
+      <c r="B87" t="s">
+        <v>310</v>
+      </c>
+      <c r="C87" t="s">
+        <v>180</v>
+      </c>
+      <c r="D87">
+        <v>3</v>
+      </c>
+      <c r="E87" t="s">
+        <v>195</v>
+      </c>
+      <c r="F87" t="s">
+        <v>311</v>
+      </c>
+      <c r="G87" t="s">
+        <v>312</v>
+      </c>
+      <c r="H87" t="s">
+        <v>28</v>
+      </c>
+      <c r="I87">
+        <v>1800</v>
+      </c>
+      <c r="J87" t="s">
+        <v>313</v>
+      </c>
+    </row>
+    <row r="88" spans="1:10" x14ac:dyDescent="0.25">
+      <c r="A88" t="s">
+        <v>286</v>
+      </c>
+      <c r="B88" t="s">
+        <v>177</v>
+      </c>
+      <c r="C88" t="s">
+        <v>214</v>
+      </c>
+      <c r="D88">
+        <v>2</v>
+      </c>
+      <c r="E88" t="s">
+        <v>314</v>
+      </c>
+      <c r="F88" t="s">
+        <v>315</v>
+      </c>
+      <c r="G88" t="s">
+        <v>316</v>
+      </c>
+      <c r="H88" t="s">
+        <v>14</v>
+      </c>
+      <c r="I88">
+        <v>500</v>
+      </c>
+      <c r="J88" t="s">
+        <v>317</v>
       </c>
     </row>
   </sheetData>

--- a/99 - Excels/LP-Register.xlsx
+++ b/99 - Excels/LP-Register.xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\Mao8ct\Desktop\PyAutomateSAP\99 - Excels\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{2402DF41-D65B-4F0E-8E9D-B2D1FF852920}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{3760916C-9292-43A5-B3E3-A552D7A48A28}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="-120" yWindow="-120" windowWidth="29040" windowHeight="17520" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
@@ -33,7 +33,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="43" uniqueCount="40">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="107" uniqueCount="73">
   <si>
     <t>Responsável</t>
   </si>
@@ -71,88 +71,187 @@
     <t>CtP/MFE31</t>
   </si>
   <si>
-    <t>REGIMARA</t>
-  </si>
-  <si>
     <t>CtP/TEF11</t>
   </si>
   <si>
     <t>-</t>
   </si>
   <si>
-    <t>SO/OPM-TS23-BR</t>
-  </si>
-  <si>
     <t>685411</t>
   </si>
   <si>
-    <t>CtP/ETS</t>
-  </si>
-  <si>
-    <t>Thais Fischer</t>
-  </si>
-  <si>
     <t>19</t>
   </si>
   <si>
-    <t>PARAFUSOS</t>
-  </si>
-  <si>
-    <t>parafuso</t>
-  </si>
-  <si>
-    <t>JULIANA MELO</t>
-  </si>
-  <si>
-    <t>LP-059958</t>
-  </si>
-  <si>
-    <t>Joao Franca</t>
-  </si>
-  <si>
-    <t>685701</t>
-  </si>
-  <si>
-    <t>4711801738</t>
-  </si>
-  <si>
-    <t>HOLDER</t>
-  </si>
-  <si>
-    <t>LP-059963</t>
-  </si>
-  <si>
     <t>Edson Bento</t>
   </si>
   <si>
-    <t>685618</t>
-  </si>
-  <si>
     <t>N/A</t>
   </si>
   <si>
-    <t>Dispositivo de sacar</t>
-  </si>
-  <si>
-    <t>OLU8CT</t>
-  </si>
-  <si>
-    <t>LP-059965</t>
-  </si>
-  <si>
     <t>Renato Meira</t>
   </si>
   <si>
-    <t>685608</t>
-  </si>
-  <si>
-    <t>Desenhos castanhas Corpo CRIN</t>
-  </si>
-  <si>
-    <t>LAL9CT</t>
-  </si>
-  <si>
-    <t>LP-059982</t>
+    <t>Yesica Gonzalez</t>
+  </si>
+  <si>
+    <t>4712004414</t>
+  </si>
+  <si>
+    <t>DU 685411 Dispositivo alimentador HTTs</t>
+  </si>
+  <si>
+    <t>DONI- 2803</t>
+  </si>
+  <si>
+    <t>LP-059983</t>
+  </si>
+  <si>
+    <t>Rafael Lima</t>
+  </si>
+  <si>
+    <t>685664</t>
+  </si>
+  <si>
+    <t>CORPO 1</t>
+  </si>
+  <si>
+    <t>BRUNO ARAUJO</t>
+  </si>
+  <si>
+    <t>LP-059984</t>
+  </si>
+  <si>
+    <t>CORPO 2</t>
+  </si>
+  <si>
+    <t>LP-059985</t>
+  </si>
+  <si>
+    <t>685557</t>
+  </si>
+  <si>
+    <t>05</t>
+  </si>
+  <si>
+    <t>4711201517</t>
+  </si>
+  <si>
+    <t>Recondicionamento</t>
+  </si>
+  <si>
+    <t>TKC1CT</t>
+  </si>
+  <si>
+    <t>SO/OPM-TS21-BR</t>
+  </si>
+  <si>
+    <t>LP-059986</t>
+  </si>
+  <si>
+    <t>4711201518</t>
+  </si>
+  <si>
+    <t>LP-059987</t>
+  </si>
+  <si>
+    <t>Marcelo Simoes</t>
+  </si>
+  <si>
+    <t>685541</t>
+  </si>
+  <si>
+    <t/>
+  </si>
+  <si>
+    <t>Pinça 17mm</t>
+  </si>
+  <si>
+    <t>DOUGLAS</t>
+  </si>
+  <si>
+    <t>LP-059993</t>
+  </si>
+  <si>
+    <t>685071</t>
+  </si>
+  <si>
+    <t>4729112324</t>
+  </si>
+  <si>
+    <t>Dispostivo para medição do elemento S3</t>
+  </si>
+  <si>
+    <t>QMM61-ANDREW</t>
+  </si>
+  <si>
+    <t>PS/QMM12-CtP</t>
+  </si>
+  <si>
+    <t>LP-059994</t>
+  </si>
+  <si>
+    <t>685485</t>
+  </si>
+  <si>
+    <t>4729112082</t>
+  </si>
+  <si>
+    <t>LE 685485 Pito SW22 para torquímetro</t>
+  </si>
+  <si>
+    <t>LP-059995</t>
+  </si>
+  <si>
+    <t>4712004763</t>
+  </si>
+  <si>
+    <t>IP 685485 Base carro alimentador IP-LE</t>
+  </si>
+  <si>
+    <t>LP-059996</t>
+  </si>
+  <si>
+    <t>685617</t>
+  </si>
+  <si>
+    <t>RETRABALHO DISCOS WOLTERS - 4717600134</t>
+  </si>
+  <si>
+    <t>HENRIQUE O.</t>
+  </si>
+  <si>
+    <t>LP-059997</t>
+  </si>
+  <si>
+    <t>685070</t>
+  </si>
+  <si>
+    <t>03</t>
+  </si>
+  <si>
+    <t>432910615</t>
+  </si>
+  <si>
+    <t>Cabeçote</t>
+  </si>
+  <si>
+    <t>SAL5CT</t>
+  </si>
+  <si>
+    <t>CtP/MFW12-A</t>
+  </si>
+  <si>
+    <t>LP-060000</t>
+  </si>
+  <si>
+    <t>4712004524</t>
+  </si>
+  <si>
+    <t>Suporte pistão TICS</t>
+  </si>
+  <si>
+    <t>LP-060001</t>
   </si>
 </sst>
 </file>
@@ -516,16 +615,16 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0000-000000000000}">
-  <dimension ref="A1:K5"/>
+  <dimension ref="A1:K13"/>
   <sheetFormatPr defaultRowHeight="15" x14ac:dyDescent="0.25"/>
   <cols>
-    <col min="1" max="1" width="12.85546875" bestFit="1" customWidth="1"/>
+    <col min="1" max="1" width="15.140625" bestFit="1" customWidth="1"/>
     <col min="2" max="2" width="20" bestFit="1" customWidth="1"/>
     <col min="3" max="3" width="20.28515625" bestFit="1" customWidth="1"/>
     <col min="4" max="4" width="11.42578125" bestFit="1" customWidth="1"/>
     <col min="5" max="5" width="12.28515625" bestFit="1" customWidth="1"/>
-    <col min="6" max="6" width="29.85546875" bestFit="1" customWidth="1"/>
-    <col min="7" max="7" width="14" bestFit="1" customWidth="1"/>
+    <col min="6" max="6" width="40.7109375" bestFit="1" customWidth="1"/>
+    <col min="7" max="7" width="16.7109375" bestFit="1" customWidth="1"/>
     <col min="8" max="8" width="21.5703125" bestFit="1" customWidth="1"/>
     <col min="9" max="9" width="14.85546875" bestFit="1" customWidth="1"/>
     <col min="10" max="10" width="13.42578125" bestFit="1" customWidth="1"/>
@@ -569,16 +668,16 @@
     </row>
     <row r="2" spans="1:11" x14ac:dyDescent="0.25">
       <c r="A2" t="s">
-        <v>18</v>
+        <v>19</v>
       </c>
       <c r="B2" t="s">
-        <v>16</v>
+        <v>14</v>
       </c>
       <c r="C2" t="s">
-        <v>19</v>
+        <v>15</v>
       </c>
       <c r="D2">
-        <v>50</v>
+        <v>1</v>
       </c>
       <c r="E2" t="s">
         <v>20</v>
@@ -590,10 +689,10 @@
         <v>22</v>
       </c>
       <c r="H2" t="s">
-        <v>15</v>
+        <v>12</v>
       </c>
       <c r="I2">
-        <v>1000</v>
+        <v>1250</v>
       </c>
       <c r="J2" t="s">
         <v>23</v>
@@ -607,25 +706,25 @@
         <v>25</v>
       </c>
       <c r="C3" t="s">
-        <v>19</v>
+        <v>15</v>
       </c>
       <c r="D3">
         <v>1</v>
       </c>
       <c r="E3" t="s">
+        <v>17</v>
+      </c>
+      <c r="F3" t="s">
         <v>26</v>
       </c>
-      <c r="F3" t="s">
+      <c r="G3" t="s">
         <v>27</v>
       </c>
-      <c r="G3" t="s">
+      <c r="H3" t="s">
         <v>12</v>
       </c>
-      <c r="H3" t="s">
-        <v>13</v>
-      </c>
       <c r="I3">
-        <v>500</v>
+        <v>337.5</v>
       </c>
       <c r="J3" t="s">
         <v>28</v>
@@ -633,66 +732,322 @@
     </row>
     <row r="4" spans="1:11" x14ac:dyDescent="0.25">
       <c r="A4" t="s">
-        <v>29</v>
+        <v>24</v>
       </c>
       <c r="B4" t="s">
-        <v>30</v>
+        <v>25</v>
       </c>
       <c r="C4" t="s">
-        <v>19</v>
+        <v>15</v>
       </c>
       <c r="D4">
         <v>1</v>
       </c>
       <c r="E4" t="s">
-        <v>31</v>
+        <v>17</v>
       </c>
       <c r="F4" t="s">
-        <v>32</v>
+        <v>29</v>
       </c>
       <c r="G4" t="s">
-        <v>33</v>
+        <v>27</v>
       </c>
       <c r="H4" t="s">
-        <v>17</v>
+        <v>12</v>
       </c>
       <c r="I4">
-        <v>200</v>
+        <v>337.5</v>
       </c>
       <c r="J4" t="s">
-        <v>34</v>
+        <v>30</v>
       </c>
     </row>
     <row r="5" spans="1:11" x14ac:dyDescent="0.25">
       <c r="A5" t="s">
+        <v>19</v>
+      </c>
+      <c r="B5" t="s">
+        <v>31</v>
+      </c>
+      <c r="C5" t="s">
+        <v>32</v>
+      </c>
+      <c r="D5">
+        <v>4</v>
+      </c>
+      <c r="E5" t="s">
+        <v>33</v>
+      </c>
+      <c r="F5" t="s">
+        <v>34</v>
+      </c>
+      <c r="G5" t="s">
         <v>35</v>
       </c>
-      <c r="B5" t="s">
+      <c r="H5" t="s">
         <v>36</v>
       </c>
-      <c r="C5" t="s">
+      <c r="I5">
+        <v>6000</v>
+      </c>
+      <c r="J5" t="s">
+        <v>37</v>
+      </c>
+    </row>
+    <row r="6" spans="1:11" x14ac:dyDescent="0.25">
+      <c r="A6" t="s">
         <v>19</v>
       </c>
-      <c r="D5">
+      <c r="B6" t="s">
+        <v>31</v>
+      </c>
+      <c r="C6" t="s">
+        <v>32</v>
+      </c>
+      <c r="D6">
+        <v>4</v>
+      </c>
+      <c r="E6" t="s">
+        <v>38</v>
+      </c>
+      <c r="F6" t="s">
+        <v>34</v>
+      </c>
+      <c r="G6" t="s">
+        <v>35</v>
+      </c>
+      <c r="H6" t="s">
+        <v>36</v>
+      </c>
+      <c r="I6">
+        <v>6000</v>
+      </c>
+      <c r="J6" t="s">
+        <v>39</v>
+      </c>
+    </row>
+    <row r="7" spans="1:11" x14ac:dyDescent="0.25">
+      <c r="A7" t="s">
+        <v>40</v>
+      </c>
+      <c r="B7" t="s">
+        <v>41</v>
+      </c>
+      <c r="C7" t="s">
+        <v>15</v>
+      </c>
+      <c r="D7">
+        <v>2</v>
+      </c>
+      <c r="E7" t="s">
+        <v>42</v>
+      </c>
+      <c r="F7" t="s">
+        <v>43</v>
+      </c>
+      <c r="G7" t="s">
+        <v>44</v>
+      </c>
+      <c r="H7" t="s">
+        <v>12</v>
+      </c>
+      <c r="I7">
+        <v>600</v>
+      </c>
+      <c r="J7" t="s">
+        <v>45</v>
+      </c>
+    </row>
+    <row r="8" spans="1:11" x14ac:dyDescent="0.25">
+      <c r="A8" t="s">
+        <v>40</v>
+      </c>
+      <c r="B8" t="s">
+        <v>46</v>
+      </c>
+      <c r="C8" t="s">
+        <v>32</v>
+      </c>
+      <c r="D8">
         <v>1</v>
       </c>
-      <c r="E5" t="s">
-        <v>14</v>
-      </c>
-      <c r="F5" t="s">
-        <v>37</v>
-      </c>
-      <c r="G5" t="s">
-        <v>38</v>
-      </c>
-      <c r="H5" t="s">
+      <c r="E8" t="s">
+        <v>47</v>
+      </c>
+      <c r="F8" t="s">
+        <v>48</v>
+      </c>
+      <c r="G8" t="s">
+        <v>49</v>
+      </c>
+      <c r="H8" t="s">
+        <v>50</v>
+      </c>
+      <c r="I8">
+        <v>1000</v>
+      </c>
+      <c r="J8" t="s">
+        <v>51</v>
+      </c>
+    </row>
+    <row r="9" spans="1:11" x14ac:dyDescent="0.25">
+      <c r="A9" t="s">
+        <v>19</v>
+      </c>
+      <c r="B9" t="s">
+        <v>52</v>
+      </c>
+      <c r="C9" t="s">
+        <v>15</v>
+      </c>
+      <c r="D9">
+        <v>2</v>
+      </c>
+      <c r="E9" t="s">
+        <v>53</v>
+      </c>
+      <c r="F9" t="s">
+        <v>54</v>
+      </c>
+      <c r="G9" t="s">
+        <v>22</v>
+      </c>
+      <c r="H9" t="s">
+        <v>12</v>
+      </c>
+      <c r="I9">
+        <v>1440</v>
+      </c>
+      <c r="J9" t="s">
+        <v>55</v>
+      </c>
+    </row>
+    <row r="10" spans="1:11" x14ac:dyDescent="0.25">
+      <c r="A10" t="s">
+        <v>19</v>
+      </c>
+      <c r="B10" t="s">
+        <v>52</v>
+      </c>
+      <c r="C10" t="s">
+        <v>15</v>
+      </c>
+      <c r="D10">
+        <v>1</v>
+      </c>
+      <c r="E10" t="s">
+        <v>56</v>
+      </c>
+      <c r="F10" t="s">
+        <v>57</v>
+      </c>
+      <c r="G10" t="s">
+        <v>22</v>
+      </c>
+      <c r="H10" t="s">
+        <v>12</v>
+      </c>
+      <c r="I10">
+        <v>5960</v>
+      </c>
+      <c r="J10" t="s">
+        <v>58</v>
+      </c>
+    </row>
+    <row r="11" spans="1:11" x14ac:dyDescent="0.25">
+      <c r="A11" t="s">
+        <v>16</v>
+      </c>
+      <c r="B11" t="s">
+        <v>59</v>
+      </c>
+      <c r="C11" t="s">
+        <v>15</v>
+      </c>
+      <c r="D11">
+        <v>6</v>
+      </c>
+      <c r="E11" t="s">
+        <v>13</v>
+      </c>
+      <c r="F11" t="s">
+        <v>60</v>
+      </c>
+      <c r="G11" t="s">
+        <v>61</v>
+      </c>
+      <c r="H11" t="s">
         <v>11</v>
       </c>
-      <c r="I5">
-        <v>1440</v>
-      </c>
-      <c r="J5" t="s">
-        <v>39</v>
+      <c r="I11">
+        <v>3000</v>
+      </c>
+      <c r="J11" t="s">
+        <v>62</v>
+      </c>
+    </row>
+    <row r="12" spans="1:11" x14ac:dyDescent="0.25">
+      <c r="A12" t="s">
+        <v>18</v>
+      </c>
+      <c r="B12" t="s">
+        <v>63</v>
+      </c>
+      <c r="C12" t="s">
+        <v>64</v>
+      </c>
+      <c r="D12">
+        <v>1</v>
+      </c>
+      <c r="E12" t="s">
+        <v>65</v>
+      </c>
+      <c r="F12" t="s">
+        <v>66</v>
+      </c>
+      <c r="G12" t="s">
+        <v>67</v>
+      </c>
+      <c r="H12" t="s">
+        <v>68</v>
+      </c>
+      <c r="I12">
+        <v>1920</v>
+      </c>
+      <c r="J12" t="s">
+        <v>69</v>
+      </c>
+    </row>
+    <row r="13" spans="1:11" x14ac:dyDescent="0.25">
+      <c r="A13" t="s">
+        <v>18</v>
+      </c>
+      <c r="B13" t="s">
+        <v>63</v>
+      </c>
+      <c r="C13" t="s">
+        <v>64</v>
+      </c>
+      <c r="D13">
+        <v>1</v>
+      </c>
+      <c r="E13" t="s">
+        <v>70</v>
+      </c>
+      <c r="F13" t="s">
+        <v>71</v>
+      </c>
+      <c r="G13" t="s">
+        <v>67</v>
+      </c>
+      <c r="H13" t="s">
+        <v>68</v>
+      </c>
+      <c r="I13">
+        <v>240</v>
+      </c>
+      <c r="J13" t="s">
+        <v>72</v>
       </c>
     </row>
   </sheetData>
